--- a/ICC005/20230703/scatt/F8_scatt.xlsx
+++ b/ICC005/20230703/scatt/F8_scatt.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C748"/>
+  <dimension ref="A1:C630"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>127</v>
+        <v>162</v>
       </c>
       <c r="C2" t="n">
-        <v>39</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="C3" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="C4" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>84</v>
+        <v>124</v>
       </c>
       <c r="C6" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>75</v>
+        <v>121</v>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>82</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>33</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="C9" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -556,10 +556,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>93</v>
+        <v>132</v>
       </c>
       <c r="C10" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -569,10 +569,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="C11" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>126</v>
+        <v>102</v>
       </c>
       <c r="C13" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14">
@@ -608,10 +608,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>100</v>
+        <v>142</v>
       </c>
       <c r="C14" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>92</v>
+        <v>125</v>
       </c>
       <c r="C15" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
@@ -634,10 +634,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -647,10 +647,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>88</v>
+        <v>133</v>
       </c>
       <c r="C17" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C18" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -673,10 +673,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="C19" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20">
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C20" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
@@ -699,10 +699,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C21" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22">
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>96</v>
+        <v>129</v>
       </c>
       <c r="C22" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23">
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="C23" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24">
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="C24" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25">
@@ -751,10 +751,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="C25" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26">
@@ -764,10 +764,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C26" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
@@ -777,10 +777,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="C27" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28">
@@ -790,10 +790,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>144</v>
+        <v>114</v>
       </c>
       <c r="C28" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29">
@@ -803,10 +803,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="C29" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="30">
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>158</v>
+        <v>117</v>
       </c>
       <c r="C30" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>67</v>
+        <v>103</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="32">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="C32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="33">
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="C33" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34">
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="C34" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
     </row>
     <row r="35">
@@ -881,10 +881,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="C35" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="36">
@@ -894,10 +894,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>105</v>
+        <v>145</v>
       </c>
       <c r="C36" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="C37" t="n">
-        <v>39</v>
+        <v>18</v>
       </c>
     </row>
     <row r="38">
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>117</v>
+        <v>147</v>
       </c>
       <c r="C38" t="n">
-        <v>39</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>109</v>
+        <v>130</v>
       </c>
       <c r="C39" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="C40" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="C41" t="n">
-        <v>34</v>
+        <v>9</v>
       </c>
     </row>
     <row r="42">
@@ -972,10 +972,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="C42" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
     </row>
     <row r="43">
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>115</v>
+        <v>137</v>
       </c>
       <c r="C43" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="44">
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="C44" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45">
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>112</v>
+        <v>134</v>
       </c>
       <c r="C45" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>103</v>
+        <v>144</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>152</v>
+        <v>120</v>
       </c>
       <c r="C47" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48">
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C48" t="n">
         <v>6</v>
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C49" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="50">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C50" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="51">
@@ -1089,10 +1089,10 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>74</v>
+        <v>126</v>
       </c>
       <c r="C51" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="52">
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>103</v>
+        <v>137</v>
       </c>
       <c r="C52" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="53">
@@ -1115,10 +1115,10 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="C53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54">
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>117</v>
+        <v>140</v>
       </c>
       <c r="C54" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="55">
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>98</v>
+        <v>139</v>
       </c>
       <c r="C55" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="56">
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>98</v>
+        <v>131</v>
       </c>
       <c r="C56" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
     </row>
     <row r="57">
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="C57" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
     </row>
     <row r="58">
@@ -1180,10 +1180,10 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>79</v>
+        <v>120</v>
       </c>
       <c r="C58" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="59">
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>66</v>
+        <v>124</v>
       </c>
       <c r="C59" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
     </row>
     <row r="60">
@@ -1206,10 +1206,10 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="C60" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61">
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="C61" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="62">
@@ -1232,10 +1232,10 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>156</v>
+        <v>131</v>
       </c>
       <c r="C62" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="C63" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="64">
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="C64" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -1271,10 +1271,10 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="C65" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="66">
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="C66" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="67">
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>72</v>
+        <v>106</v>
       </c>
       <c r="C67" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="68">
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>77</v>
+        <v>128</v>
       </c>
       <c r="C68" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69">
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="C69" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="70">
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>86</v>
+        <v>119</v>
       </c>
       <c r="C70" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71">
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="C71" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="72">
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="C72" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="73">
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>147</v>
+        <v>120</v>
       </c>
       <c r="C73" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="74">
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C74" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="75">
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>124</v>
+        <v>149</v>
       </c>
       <c r="C75" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>85</v>
+        <v>123</v>
       </c>
       <c r="C76" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="77">
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>98</v>
+        <v>126</v>
       </c>
       <c r="C77" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="78">
@@ -1440,10 +1440,10 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>112</v>
+        <v>142</v>
       </c>
       <c r="C78" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="79">
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>114</v>
+        <v>152</v>
       </c>
       <c r="C79" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
@@ -1466,10 +1466,10 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="C80" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="81">
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C81" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="82">
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="C82" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="83">
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>68</v>
+        <v>131</v>
       </c>
       <c r="C83" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
     </row>
     <row r="84">
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="C84" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
     </row>
     <row r="85">
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C85" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="86">
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="C86" t="n">
-        <v>36</v>
+        <v>22</v>
       </c>
     </row>
     <row r="87">
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>102</v>
+        <v>136</v>
       </c>
       <c r="C87" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
     </row>
     <row r="88">
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="C88" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="89">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="C89" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="90">
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>105</v>
+        <v>136</v>
       </c>
       <c r="C90" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="91">
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="C91" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="92">
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>106</v>
+        <v>128</v>
       </c>
       <c r="C92" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="93">
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>113</v>
+        <v>138</v>
       </c>
       <c r="C93" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
     </row>
     <row r="94">
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>136</v>
+        <v>117</v>
       </c>
       <c r="C94" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="95">
@@ -1661,10 +1661,10 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="C95" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="96">
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>102</v>
+        <v>139</v>
       </c>
       <c r="C96" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>82</v>
+        <v>148</v>
       </c>
       <c r="C97" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="C98" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="99">
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>95</v>
+        <v>133</v>
       </c>
       <c r="C99" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
     </row>
     <row r="100">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>100</v>
+        <v>128</v>
       </c>
       <c r="C100" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
     </row>
     <row r="101">
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="C101" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
     </row>
     <row r="102">
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="C102" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
     </row>
     <row r="103">
@@ -1765,7 +1765,7 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="C103" t="n">
         <v>19</v>
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C104" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
     </row>
     <row r="105">
@@ -1791,7 +1791,7 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="C105" t="n">
         <v>13</v>
@@ -1804,10 +1804,10 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="C106" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="107">
@@ -1817,10 +1817,10 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C107" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="108">
@@ -1830,10 +1830,10 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="C108" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="109">
@@ -1843,10 +1843,10 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="C109" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
     </row>
     <row r="110">
@@ -1856,10 +1856,10 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>97</v>
+        <v>134</v>
       </c>
       <c r="C110" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="111">
@@ -1869,10 +1869,10 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>89</v>
+        <v>149</v>
       </c>
       <c r="C111" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="112">
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>103</v>
+        <v>136</v>
       </c>
       <c r="C112" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="113">
@@ -1895,10 +1895,10 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="C113" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
     </row>
     <row r="114">
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="C114" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="115">
@@ -1921,10 +1921,10 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>99</v>
+        <v>128</v>
       </c>
       <c r="C115" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="116">
@@ -1934,10 +1934,10 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C116" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
     </row>
     <row r="117">
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="C117" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
     </row>
     <row r="118">
@@ -1960,10 +1960,10 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="C118" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="119">
@@ -1973,10 +1973,10 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C119" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="120">
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>92</v>
+        <v>116</v>
       </c>
       <c r="C120" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
     </row>
     <row r="121">
@@ -1999,10 +1999,10 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="C121" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="122">
@@ -2012,10 +2012,10 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="C122" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="123">
@@ -2025,10 +2025,10 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="C123" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="124">
@@ -2038,10 +2038,10 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>72</v>
+        <v>140</v>
       </c>
       <c r="C124" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="125">
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="C125" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="126">
@@ -2064,10 +2064,10 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C126" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
     </row>
     <row r="127">
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="C127" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="128">
@@ -2090,10 +2090,10 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="C128" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
     </row>
     <row r="129">
@@ -2103,10 +2103,10 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>88</v>
+        <v>125</v>
       </c>
       <c r="C129" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="130">
@@ -2116,10 +2116,10 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>49</v>
+        <v>134</v>
       </c>
       <c r="C130" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
     </row>
     <row r="131">
@@ -2129,10 +2129,10 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="C131" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="132">
@@ -2142,10 +2142,10 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="C132" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="133">
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="C133" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="134">
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="C134" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="135">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="C135" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="136">
@@ -2194,10 +2194,10 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>97</v>
+        <v>131</v>
       </c>
       <c r="C136" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="137">
@@ -2207,10 +2207,10 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C137" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="138">
@@ -2220,10 +2220,10 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="C138" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="139">
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="C139" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
     </row>
     <row r="140">
@@ -2246,10 +2246,10 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>105</v>
+        <v>146</v>
       </c>
       <c r="C140" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="141">
@@ -2262,7 +2262,7 @@
         <v>111</v>
       </c>
       <c r="C141" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="142">
@@ -2272,10 +2272,10 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>147</v>
+        <v>118</v>
       </c>
       <c r="C142" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="143">
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="C143" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
     </row>
     <row r="144">
@@ -2298,10 +2298,10 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="C144" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="145">
@@ -2311,10 +2311,10 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>113</v>
+        <v>144</v>
       </c>
       <c r="C145" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="146">
@@ -2324,10 +2324,10 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>82</v>
+        <v>145</v>
       </c>
       <c r="C146" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
@@ -2337,10 +2337,10 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C147" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="148">
@@ -2350,10 +2350,10 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>104</v>
+        <v>149</v>
       </c>
       <c r="C148" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
@@ -2363,10 +2363,10 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="C149" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="150">
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="C150" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
     </row>
     <row r="151">
@@ -2389,10 +2389,10 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="C151" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="152">
@@ -2402,10 +2402,10 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="C152" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="153">
@@ -2415,10 +2415,10 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="C153" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
     </row>
     <row r="154">
@@ -2428,10 +2428,10 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>99</v>
+        <v>137</v>
       </c>
       <c r="C154" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
     </row>
     <row r="155">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>112</v>
+        <v>134</v>
       </c>
       <c r="C155" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="156">
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C156" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="157">
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C157" t="n">
         <v>18</v>
@@ -2480,10 +2480,10 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="C158" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="159">
@@ -2493,10 +2493,10 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>168</v>
+        <v>130</v>
       </c>
       <c r="C159" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="160">
@@ -2506,10 +2506,10 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="C160" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="161">
@@ -2519,7 +2519,7 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C161" t="n">
         <v>0</v>
@@ -2532,10 +2532,10 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="C162" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
     </row>
     <row r="163">
@@ -2545,10 +2545,10 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="C163" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="164">
@@ -2558,10 +2558,10 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C164" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="165">
@@ -2571,10 +2571,10 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="C165" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
     </row>
     <row r="166">
@@ -2584,10 +2584,10 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="C166" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="167">
@@ -2597,10 +2597,10 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="C167" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
     </row>
     <row r="168">
@@ -2610,10 +2610,10 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="C168" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="169">
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="C169" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
     </row>
     <row r="170">
@@ -2636,10 +2636,10 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="C170" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="171">
@@ -2649,10 +2649,10 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="C171" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="172">
@@ -2662,10 +2662,10 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="C172" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
     </row>
     <row r="173">
@@ -2675,10 +2675,10 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C173" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="174">
@@ -2688,10 +2688,10 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="C174" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="175">
@@ -2701,10 +2701,10 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>116</v>
+        <v>131</v>
       </c>
       <c r="C175" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="176">
@@ -2714,7 +2714,7 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>100</v>
+        <v>134</v>
       </c>
       <c r="C176" t="n">
         <v>18</v>
@@ -2727,10 +2727,10 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>116</v>
+        <v>142</v>
       </c>
       <c r="C177" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
     </row>
     <row r="178">
@@ -2740,10 +2740,10 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>156</v>
+        <v>132</v>
       </c>
       <c r="C178" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="179">
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="C179" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="180">
@@ -2766,10 +2766,10 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="C180" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="181">
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>105</v>
+        <v>140</v>
       </c>
       <c r="C181" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
     </row>
     <row r="182">
@@ -2792,10 +2792,10 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="C182" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="183">
@@ -2805,7 +2805,7 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C183" t="n">
         <v>9</v>
@@ -2818,10 +2818,10 @@
         </is>
       </c>
       <c r="B184" t="n">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="C184" t="n">
-        <v>35</v>
+        <v>13</v>
       </c>
     </row>
     <row r="185">
@@ -2831,10 +2831,10 @@
         </is>
       </c>
       <c r="B185" t="n">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="C185" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="186">
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="C186" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="187">
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="B187" t="n">
-        <v>119</v>
+        <v>141</v>
       </c>
       <c r="C187" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
     </row>
     <row r="188">
@@ -2870,10 +2870,10 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="C188" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="189">
@@ -2883,10 +2883,10 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="C189" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="190">
@@ -2896,10 +2896,10 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>93</v>
+        <v>120</v>
       </c>
       <c r="C190" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="191">
@@ -2909,10 +2909,10 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>95</v>
+        <v>135</v>
       </c>
       <c r="C191" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="192">
@@ -2922,10 +2922,10 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="C192" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
     </row>
     <row r="193">
@@ -2935,10 +2935,10 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="C193" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="194">
@@ -2948,10 +2948,10 @@
         </is>
       </c>
       <c r="B194" t="n">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="C194" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="195">
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>94</v>
+        <v>131</v>
       </c>
       <c r="C195" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
     </row>
     <row r="196">
@@ -2974,10 +2974,10 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="C196" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197">
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="C197" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
     </row>
     <row r="198">
@@ -3000,7 +3000,7 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="C198" t="n">
         <v>12</v>
@@ -3013,10 +3013,10 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>114</v>
+        <v>159</v>
       </c>
       <c r="C199" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
     </row>
     <row r="200">
@@ -3026,10 +3026,10 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="C200" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="201">
@@ -3039,10 +3039,10 @@
         </is>
       </c>
       <c r="B201" t="n">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="C201" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="202">
@@ -3052,10 +3052,10 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>108</v>
+        <v>144</v>
       </c>
       <c r="C202" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="203">
@@ -3065,7 +3065,7 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>82</v>
+        <v>132</v>
       </c>
       <c r="C203" t="n">
         <v>4</v>
@@ -3078,10 +3078,10 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="C204" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="205">
@@ -3091,10 +3091,10 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>114</v>
+        <v>136</v>
       </c>
       <c r="C205" t="n">
-        <v>48</v>
+        <v>19</v>
       </c>
     </row>
     <row r="206">
@@ -3104,10 +3104,10 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C206" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="207">
@@ -3117,10 +3117,10 @@
         </is>
       </c>
       <c r="B207" t="n">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="C207" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="208">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="B208" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C208" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
     </row>
     <row r="209">
@@ -3143,10 +3143,10 @@
         </is>
       </c>
       <c r="B209" t="n">
-        <v>129</v>
+        <v>162</v>
       </c>
       <c r="C209" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="210">
@@ -3156,10 +3156,10 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="C210" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="211">
@@ -3169,7 +3169,7 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="C211" t="n">
         <v>14</v>
@@ -3182,10 +3182,10 @@
         </is>
       </c>
       <c r="B212" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C212" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="213">
@@ -3195,10 +3195,10 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="C213" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="214">
@@ -3208,7 +3208,7 @@
         </is>
       </c>
       <c r="B214" t="n">
-        <v>86</v>
+        <v>126</v>
       </c>
       <c r="C214" t="n">
         <v>17</v>
@@ -3221,10 +3221,10 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="C215" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
     </row>
     <row r="216">
@@ -3234,10 +3234,10 @@
         </is>
       </c>
       <c r="B216" t="n">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C216" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="217">
@@ -3247,10 +3247,10 @@
         </is>
       </c>
       <c r="B217" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C217" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="218">
@@ -3260,7 +3260,7 @@
         </is>
       </c>
       <c r="B218" t="n">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="C218" t="n">
         <v>0</v>
@@ -3273,10 +3273,10 @@
         </is>
       </c>
       <c r="B219" t="n">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="C219" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
     </row>
     <row r="220">
@@ -3286,10 +3286,10 @@
         </is>
       </c>
       <c r="B220" t="n">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="C220" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="221">
@@ -3299,10 +3299,10 @@
         </is>
       </c>
       <c r="B221" t="n">
-        <v>100</v>
+        <v>146</v>
       </c>
       <c r="C221" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="222">
@@ -3312,10 +3312,10 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C222" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="223">
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="B223" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C223" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
     </row>
     <row r="224">
@@ -3338,10 +3338,10 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="C224" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
     </row>
     <row r="225">
@@ -3351,10 +3351,10 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="C225" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
     </row>
     <row r="226">
@@ -3367,7 +3367,7 @@
         <v>120</v>
       </c>
       <c r="C226" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="227">
@@ -3377,10 +3377,10 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>99</v>
+        <v>147</v>
       </c>
       <c r="C227" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
     </row>
     <row r="228">
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>105</v>
+        <v>137</v>
       </c>
       <c r="C228" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="229">
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="B229" t="n">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="C229" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="230">
@@ -3416,10 +3416,10 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>165</v>
+        <v>140</v>
       </c>
       <c r="C230" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="231">
@@ -3429,10 +3429,10 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="C231" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="232">
@@ -3442,10 +3442,10 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>86</v>
+        <v>132</v>
       </c>
       <c r="C232" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="233">
@@ -3455,10 +3455,10 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>111</v>
+        <v>136</v>
       </c>
       <c r="C233" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="234">
@@ -3468,10 +3468,10 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="C234" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="235">
@@ -3481,10 +3481,10 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>112</v>
+        <v>140</v>
       </c>
       <c r="C235" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
     </row>
     <row r="236">
@@ -3494,10 +3494,10 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C236" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="237">
@@ -3507,10 +3507,10 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="C237" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
     </row>
     <row r="238">
@@ -3520,10 +3520,10 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="C238" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
     </row>
     <row r="239">
@@ -3533,10 +3533,10 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="C239" t="n">
-        <v>32</v>
+        <v>7</v>
       </c>
     </row>
     <row r="240">
@@ -3546,10 +3546,10 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="C240" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="241">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="C241" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="242">
@@ -3572,10 +3572,10 @@
         </is>
       </c>
       <c r="B242" t="n">
-        <v>102</v>
+        <v>133</v>
       </c>
       <c r="C242" t="n">
-        <v>39</v>
+        <v>17</v>
       </c>
     </row>
     <row r="243">
@@ -3585,10 +3585,10 @@
         </is>
       </c>
       <c r="B243" t="n">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="C243" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="244">
@@ -3598,10 +3598,10 @@
         </is>
       </c>
       <c r="B244" t="n">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="C244" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="245">
@@ -3611,10 +3611,10 @@
         </is>
       </c>
       <c r="B245" t="n">
-        <v>97</v>
+        <v>138</v>
       </c>
       <c r="C245" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
     </row>
     <row r="246">
@@ -3624,10 +3624,10 @@
         </is>
       </c>
       <c r="B246" t="n">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="C246" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="247">
@@ -3637,10 +3637,10 @@
         </is>
       </c>
       <c r="B247" t="n">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="C247" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="248">
@@ -3650,10 +3650,10 @@
         </is>
       </c>
       <c r="B248" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C248" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="249">
@@ -3663,10 +3663,10 @@
         </is>
       </c>
       <c r="B249" t="n">
-        <v>118</v>
+        <v>146</v>
       </c>
       <c r="C249" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="250">
@@ -3676,10 +3676,10 @@
         </is>
       </c>
       <c r="B250" t="n">
-        <v>128</v>
+        <v>97</v>
       </c>
       <c r="C250" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
     </row>
     <row r="251">
@@ -3689,10 +3689,10 @@
         </is>
       </c>
       <c r="B251" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="C251" t="n">
-        <v>33</v>
+        <v>15</v>
       </c>
     </row>
     <row r="252">
@@ -3702,7 +3702,7 @@
         </is>
       </c>
       <c r="B252" t="n">
-        <v>76</v>
+        <v>141</v>
       </c>
       <c r="C252" t="n">
         <v>21</v>
@@ -3715,10 +3715,10 @@
         </is>
       </c>
       <c r="B253" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C253" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="254">
@@ -3728,10 +3728,10 @@
         </is>
       </c>
       <c r="B254" t="n">
-        <v>99</v>
+        <v>127</v>
       </c>
       <c r="C254" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="255">
@@ -3741,10 +3741,10 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>104</v>
+        <v>138</v>
       </c>
       <c r="C255" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="256">
@@ -3754,10 +3754,10 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="C256" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="257">
@@ -3767,10 +3767,10 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="C257" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="258">
@@ -3780,10 +3780,10 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C258" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="259">
@@ -3793,10 +3793,10 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>116</v>
+        <v>146</v>
       </c>
       <c r="C259" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="260">
@@ -3806,10 +3806,10 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>99</v>
+        <v>122</v>
       </c>
       <c r="C260" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="261">
@@ -3819,10 +3819,10 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="C261" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="262">
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="B262" t="n">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="C262" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="263">
@@ -3845,10 +3845,10 @@
         </is>
       </c>
       <c r="B263" t="n">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="C263" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="264">
@@ -3858,10 +3858,10 @@
         </is>
       </c>
       <c r="B264" t="n">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="C264" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
     </row>
     <row r="265">
@@ -3871,10 +3871,10 @@
         </is>
       </c>
       <c r="B265" t="n">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="C265" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
     </row>
     <row r="266">
@@ -3884,10 +3884,10 @@
         </is>
       </c>
       <c r="B266" t="n">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="C266" t="n">
-        <v>39</v>
+        <v>16</v>
       </c>
     </row>
     <row r="267">
@@ -3897,10 +3897,10 @@
         </is>
       </c>
       <c r="B267" t="n">
-        <v>93</v>
+        <v>156</v>
       </c>
       <c r="C267" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="268">
@@ -3910,10 +3910,10 @@
         </is>
       </c>
       <c r="B268" t="n">
-        <v>109</v>
+        <v>146</v>
       </c>
       <c r="C268" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
     </row>
     <row r="269">
@@ -3923,10 +3923,10 @@
         </is>
       </c>
       <c r="B269" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C269" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="270">
@@ -3936,10 +3936,10 @@
         </is>
       </c>
       <c r="B270" t="n">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="C270" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="271">
@@ -3949,10 +3949,10 @@
         </is>
       </c>
       <c r="B271" t="n">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="C271" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="272">
@@ -3962,10 +3962,10 @@
         </is>
       </c>
       <c r="B272" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C272" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="273">
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="B273" t="n">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="C273" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="274">
@@ -3988,10 +3988,10 @@
         </is>
       </c>
       <c r="B274" t="n">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="C274" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
     </row>
     <row r="275">
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="B275" t="n">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="C275" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="276">
@@ -4014,10 +4014,10 @@
         </is>
       </c>
       <c r="B276" t="n">
-        <v>108</v>
+        <v>137</v>
       </c>
       <c r="C276" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="277">
@@ -4027,10 +4027,10 @@
         </is>
       </c>
       <c r="B277" t="n">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="C277" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="278">
@@ -4040,10 +4040,10 @@
         </is>
       </c>
       <c r="B278" t="n">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="C278" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="279">
@@ -4053,10 +4053,10 @@
         </is>
       </c>
       <c r="B279" t="n">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="C279" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="280">
@@ -4066,10 +4066,10 @@
         </is>
       </c>
       <c r="B280" t="n">
-        <v>93</v>
+        <v>137</v>
       </c>
       <c r="C280" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="281">
@@ -4079,10 +4079,10 @@
         </is>
       </c>
       <c r="B281" t="n">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="C281" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="282">
@@ -4092,10 +4092,10 @@
         </is>
       </c>
       <c r="B282" t="n">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="C282" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
     </row>
     <row r="283">
@@ -4105,10 +4105,10 @@
         </is>
       </c>
       <c r="B283" t="n">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="C283" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="284">
@@ -4118,10 +4118,10 @@
         </is>
       </c>
       <c r="B284" t="n">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="C284" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
     </row>
     <row r="285">
@@ -4131,10 +4131,10 @@
         </is>
       </c>
       <c r="B285" t="n">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="C285" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
     </row>
     <row r="286">
@@ -4144,10 +4144,10 @@
         </is>
       </c>
       <c r="B286" t="n">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="C286" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="287">
@@ -4157,10 +4157,10 @@
         </is>
       </c>
       <c r="B287" t="n">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="C287" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
     </row>
     <row r="288">
@@ -4170,10 +4170,10 @@
         </is>
       </c>
       <c r="B288" t="n">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="C288" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
     </row>
     <row r="289">
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="B289" t="n">
-        <v>99</v>
+        <v>128</v>
       </c>
       <c r="C289" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="290">
@@ -4196,10 +4196,10 @@
         </is>
       </c>
       <c r="B290" t="n">
-        <v>86</v>
+        <v>133</v>
       </c>
       <c r="C290" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="291">
@@ -4209,10 +4209,10 @@
         </is>
       </c>
       <c r="B291" t="n">
-        <v>110</v>
+        <v>142</v>
       </c>
       <c r="C291" t="n">
-        <v>35</v>
+        <v>14</v>
       </c>
     </row>
     <row r="292">
@@ -4222,10 +4222,10 @@
         </is>
       </c>
       <c r="B292" t="n">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="C292" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="293">
@@ -4235,10 +4235,10 @@
         </is>
       </c>
       <c r="B293" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C293" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="294">
@@ -4248,10 +4248,10 @@
         </is>
       </c>
       <c r="B294" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C294" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="295">
@@ -4261,7 +4261,7 @@
         </is>
       </c>
       <c r="B295" t="n">
-        <v>96</v>
+        <v>125</v>
       </c>
       <c r="C295" t="n">
         <v>11</v>
@@ -4274,10 +4274,10 @@
         </is>
       </c>
       <c r="B296" t="n">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="C296" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
     </row>
     <row r="297">
@@ -4287,10 +4287,10 @@
         </is>
       </c>
       <c r="B297" t="n">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="C297" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="298">
@@ -4300,10 +4300,10 @@
         </is>
       </c>
       <c r="B298" t="n">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="C298" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="299">
@@ -4313,10 +4313,10 @@
         </is>
       </c>
       <c r="B299" t="n">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C299" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="300">
@@ -4326,10 +4326,10 @@
         </is>
       </c>
       <c r="B300" t="n">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="C300" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
     </row>
     <row r="301">
@@ -4339,10 +4339,10 @@
         </is>
       </c>
       <c r="B301" t="n">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="C301" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
     </row>
     <row r="302">
@@ -4352,10 +4352,10 @@
         </is>
       </c>
       <c r="B302" t="n">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="C302" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="303">
@@ -4365,10 +4365,10 @@
         </is>
       </c>
       <c r="B303" t="n">
-        <v>86</v>
+        <v>140</v>
       </c>
       <c r="C303" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="304">
@@ -4378,10 +4378,10 @@
         </is>
       </c>
       <c r="B304" t="n">
-        <v>109</v>
+        <v>157</v>
       </c>
       <c r="C304" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="305">
@@ -4391,10 +4391,10 @@
         </is>
       </c>
       <c r="B305" t="n">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="C305" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="306">
@@ -4404,10 +4404,10 @@
         </is>
       </c>
       <c r="B306" t="n">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C306" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="307">
@@ -4417,10 +4417,10 @@
         </is>
       </c>
       <c r="B307" t="n">
-        <v>106</v>
+        <v>142</v>
       </c>
       <c r="C307" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="308">
@@ -4430,10 +4430,10 @@
         </is>
       </c>
       <c r="B308" t="n">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="C308" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
     </row>
     <row r="309">
@@ -4443,10 +4443,10 @@
         </is>
       </c>
       <c r="B309" t="n">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="C309" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
     </row>
     <row r="310">
@@ -4456,10 +4456,10 @@
         </is>
       </c>
       <c r="B310" t="n">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="C310" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="311">
@@ -4469,10 +4469,10 @@
         </is>
       </c>
       <c r="B311" t="n">
-        <v>125</v>
+        <v>145</v>
       </c>
       <c r="C311" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="312">
@@ -4482,10 +4482,10 @@
         </is>
       </c>
       <c r="B312" t="n">
-        <v>94</v>
+        <v>135</v>
       </c>
       <c r="C312" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="313">
@@ -4495,7 +4495,7 @@
         </is>
       </c>
       <c r="B313" t="n">
-        <v>127</v>
+        <v>148</v>
       </c>
       <c r="C313" t="n">
         <v>7</v>
@@ -4508,10 +4508,10 @@
         </is>
       </c>
       <c r="B314" t="n">
-        <v>97</v>
+        <v>128</v>
       </c>
       <c r="C314" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="315">
@@ -4521,10 +4521,10 @@
         </is>
       </c>
       <c r="B315" t="n">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C315" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="316">
@@ -4534,10 +4534,10 @@
         </is>
       </c>
       <c r="B316" t="n">
-        <v>119</v>
+        <v>144</v>
       </c>
       <c r="C316" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="317">
@@ -4547,10 +4547,10 @@
         </is>
       </c>
       <c r="B317" t="n">
-        <v>115</v>
+        <v>135</v>
       </c>
       <c r="C317" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
     </row>
     <row r="318">
@@ -4560,10 +4560,10 @@
         </is>
       </c>
       <c r="B318" t="n">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="C318" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
     </row>
     <row r="319">
@@ -4573,10 +4573,10 @@
         </is>
       </c>
       <c r="B319" t="n">
-        <v>87</v>
+        <v>132</v>
       </c>
       <c r="C319" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="320">
@@ -4586,10 +4586,10 @@
         </is>
       </c>
       <c r="B320" t="n">
-        <v>112</v>
+        <v>139</v>
       </c>
       <c r="C320" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="321">
@@ -4599,10 +4599,10 @@
         </is>
       </c>
       <c r="B321" t="n">
-        <v>95</v>
+        <v>124</v>
       </c>
       <c r="C321" t="n">
-        <v>47</v>
+        <v>22</v>
       </c>
     </row>
     <row r="322">
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="B322" t="n">
-        <v>73</v>
+        <v>118</v>
       </c>
       <c r="C322" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="323">
@@ -4625,10 +4625,10 @@
         </is>
       </c>
       <c r="B323" t="n">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="C323" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="324">
@@ -4638,10 +4638,10 @@
         </is>
       </c>
       <c r="B324" t="n">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="C324" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="325">
@@ -4651,10 +4651,10 @@
         </is>
       </c>
       <c r="B325" t="n">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="C325" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="326">
@@ -4664,10 +4664,10 @@
         </is>
       </c>
       <c r="B326" t="n">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="C326" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
     </row>
     <row r="327">
@@ -4677,10 +4677,10 @@
         </is>
       </c>
       <c r="B327" t="n">
-        <v>92</v>
+        <v>123</v>
       </c>
       <c r="C327" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
     </row>
     <row r="328">
@@ -4690,10 +4690,10 @@
         </is>
       </c>
       <c r="B328" t="n">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C328" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="329">
@@ -4703,10 +4703,10 @@
         </is>
       </c>
       <c r="B329" t="n">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="C329" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
     </row>
     <row r="330">
@@ -4716,10 +4716,10 @@
         </is>
       </c>
       <c r="B330" t="n">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="C330" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="331">
@@ -4729,10 +4729,10 @@
         </is>
       </c>
       <c r="B331" t="n">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="C331" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="332">
@@ -4742,10 +4742,10 @@
         </is>
       </c>
       <c r="B332" t="n">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="C332" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="333">
@@ -4755,10 +4755,10 @@
         </is>
       </c>
       <c r="B333" t="n">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="C333" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="334">
@@ -4768,10 +4768,10 @@
         </is>
       </c>
       <c r="B334" t="n">
-        <v>90</v>
+        <v>133</v>
       </c>
       <c r="C334" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="335">
@@ -4781,10 +4781,10 @@
         </is>
       </c>
       <c r="B335" t="n">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="C335" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="336">
@@ -4794,10 +4794,10 @@
         </is>
       </c>
       <c r="B336" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C336" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="337">
@@ -4807,10 +4807,10 @@
         </is>
       </c>
       <c r="B337" t="n">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="C337" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="338">
@@ -4820,10 +4820,10 @@
         </is>
       </c>
       <c r="B338" t="n">
-        <v>107</v>
+        <v>129</v>
       </c>
       <c r="C338" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="339">
@@ -4833,10 +4833,10 @@
         </is>
       </c>
       <c r="B339" t="n">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="C339" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="340">
@@ -4846,10 +4846,10 @@
         </is>
       </c>
       <c r="B340" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C340" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
     <row r="341">
@@ -4859,10 +4859,10 @@
         </is>
       </c>
       <c r="B341" t="n">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="C341" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="342">
@@ -4872,10 +4872,10 @@
         </is>
       </c>
       <c r="B342" t="n">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="C342" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="343">
@@ -4885,10 +4885,10 @@
         </is>
       </c>
       <c r="B343" t="n">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="C343" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="344">
@@ -4898,10 +4898,10 @@
         </is>
       </c>
       <c r="B344" t="n">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="C344" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="345">
@@ -4911,10 +4911,10 @@
         </is>
       </c>
       <c r="B345" t="n">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="C345" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="346">
@@ -4924,10 +4924,10 @@
         </is>
       </c>
       <c r="B346" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C346" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="347">
@@ -4937,10 +4937,10 @@
         </is>
       </c>
       <c r="B347" t="n">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="C347" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="348">
@@ -4950,10 +4950,10 @@
         </is>
       </c>
       <c r="B348" t="n">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="C348" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="349">
@@ -4966,7 +4966,7 @@
         <v>127</v>
       </c>
       <c r="C349" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="350">
@@ -4976,10 +4976,10 @@
         </is>
       </c>
       <c r="B350" t="n">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="C350" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="351">
@@ -4989,10 +4989,10 @@
         </is>
       </c>
       <c r="B351" t="n">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="C351" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="352">
@@ -5002,10 +5002,10 @@
         </is>
       </c>
       <c r="B352" t="n">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="C352" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="353">
@@ -5015,10 +5015,10 @@
         </is>
       </c>
       <c r="B353" t="n">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="C353" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="354">
@@ -5028,10 +5028,10 @@
         </is>
       </c>
       <c r="B354" t="n">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C354" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="355">
@@ -5041,10 +5041,10 @@
         </is>
       </c>
       <c r="B355" t="n">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="C355" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
     </row>
     <row r="356">
@@ -5054,10 +5054,10 @@
         </is>
       </c>
       <c r="B356" t="n">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="C356" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="357">
@@ -5067,10 +5067,10 @@
         </is>
       </c>
       <c r="B357" t="n">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="C357" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="358">
@@ -5080,10 +5080,10 @@
         </is>
       </c>
       <c r="B358" t="n">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="C358" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="359">
@@ -5093,10 +5093,10 @@
         </is>
       </c>
       <c r="B359" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C359" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="360">
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="B360" t="n">
-        <v>83</v>
+        <v>152</v>
       </c>
       <c r="C360" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="361">
@@ -5119,10 +5119,10 @@
         </is>
       </c>
       <c r="B361" t="n">
-        <v>106</v>
+        <v>143</v>
       </c>
       <c r="C361" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="362">
@@ -5132,10 +5132,10 @@
         </is>
       </c>
       <c r="B362" t="n">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="C362" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
     <row r="363">
@@ -5145,10 +5145,10 @@
         </is>
       </c>
       <c r="B363" t="n">
-        <v>132</v>
+        <v>113</v>
       </c>
       <c r="C363" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="364">
@@ -5158,10 +5158,10 @@
         </is>
       </c>
       <c r="B364" t="n">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="C364" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="365">
@@ -5171,10 +5171,10 @@
         </is>
       </c>
       <c r="B365" t="n">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C365" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="366">
@@ -5184,10 +5184,10 @@
         </is>
       </c>
       <c r="B366" t="n">
-        <v>91</v>
+        <v>144</v>
       </c>
       <c r="C366" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="367">
@@ -5197,10 +5197,10 @@
         </is>
       </c>
       <c r="B367" t="n">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="C367" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="368">
@@ -5210,10 +5210,10 @@
         </is>
       </c>
       <c r="B368" t="n">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="C368" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="369">
@@ -5223,10 +5223,10 @@
         </is>
       </c>
       <c r="B369" t="n">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="C369" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="370">
@@ -5236,10 +5236,10 @@
         </is>
       </c>
       <c r="B370" t="n">
-        <v>114</v>
+        <v>143</v>
       </c>
       <c r="C370" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
     </row>
     <row r="371">
@@ -5249,10 +5249,10 @@
         </is>
       </c>
       <c r="B371" t="n">
-        <v>95</v>
+        <v>152</v>
       </c>
       <c r="C371" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="372">
@@ -5265,7 +5265,7 @@
         <v>138</v>
       </c>
       <c r="C372" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="373">
@@ -5275,10 +5275,10 @@
         </is>
       </c>
       <c r="B373" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C373" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
     </row>
     <row r="374">
@@ -5288,10 +5288,10 @@
         </is>
       </c>
       <c r="B374" t="n">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="C374" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="375">
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="B375" t="n">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C375" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
     <row r="376">
@@ -5314,10 +5314,10 @@
         </is>
       </c>
       <c r="B376" t="n">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="C376" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="377">
@@ -5327,10 +5327,10 @@
         </is>
       </c>
       <c r="B377" t="n">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="C377" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
     </row>
     <row r="378">
@@ -5340,7 +5340,7 @@
         </is>
       </c>
       <c r="B378" t="n">
-        <v>96</v>
+        <v>133</v>
       </c>
       <c r="C378" t="n">
         <v>15</v>
@@ -5353,10 +5353,10 @@
         </is>
       </c>
       <c r="B379" t="n">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="C379" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="380">
@@ -5366,10 +5366,10 @@
         </is>
       </c>
       <c r="B380" t="n">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="C380" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="381">
@@ -5379,10 +5379,10 @@
         </is>
       </c>
       <c r="B381" t="n">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="C381" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="382">
@@ -5392,10 +5392,10 @@
         </is>
       </c>
       <c r="B382" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C382" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
     </row>
     <row r="383">
@@ -5405,10 +5405,10 @@
         </is>
       </c>
       <c r="B383" t="n">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="C383" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
     </row>
     <row r="384">
@@ -5418,10 +5418,10 @@
         </is>
       </c>
       <c r="B384" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="C384" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="385">
@@ -5431,10 +5431,10 @@
         </is>
       </c>
       <c r="B385" t="n">
-        <v>98</v>
+        <v>124</v>
       </c>
       <c r="C385" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="386">
@@ -5444,10 +5444,10 @@
         </is>
       </c>
       <c r="B386" t="n">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="C386" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="387">
@@ -5457,10 +5457,10 @@
         </is>
       </c>
       <c r="B387" t="n">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="C387" t="n">
-        <v>35</v>
+        <v>17</v>
       </c>
     </row>
     <row r="388">
@@ -5470,10 +5470,10 @@
         </is>
       </c>
       <c r="B388" t="n">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C388" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
     <row r="389">
@@ -5483,10 +5483,10 @@
         </is>
       </c>
       <c r="B389" t="n">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C389" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
     </row>
     <row r="390">
@@ -5496,10 +5496,10 @@
         </is>
       </c>
       <c r="B390" t="n">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="C390" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
     </row>
     <row r="391">
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="B391" t="n">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="C391" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
     </row>
     <row r="392">
@@ -5522,10 +5522,10 @@
         </is>
       </c>
       <c r="B392" t="n">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="C392" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="393">
@@ -5535,10 +5535,10 @@
         </is>
       </c>
       <c r="B393" t="n">
-        <v>113</v>
+        <v>136</v>
       </c>
       <c r="C393" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
     </row>
     <row r="394">
@@ -5548,10 +5548,10 @@
         </is>
       </c>
       <c r="B394" t="n">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="C394" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
     </row>
     <row r="395">
@@ -5561,10 +5561,10 @@
         </is>
       </c>
       <c r="B395" t="n">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="C395" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="396">
@@ -5574,10 +5574,10 @@
         </is>
       </c>
       <c r="B396" t="n">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C396" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="397">
@@ -5587,10 +5587,10 @@
         </is>
       </c>
       <c r="B397" t="n">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="C397" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="398">
@@ -5600,10 +5600,10 @@
         </is>
       </c>
       <c r="B398" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C398" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="399">
@@ -5613,10 +5613,10 @@
         </is>
       </c>
       <c r="B399" t="n">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="C399" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="400">
@@ -5626,10 +5626,10 @@
         </is>
       </c>
       <c r="B400" t="n">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="C400" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="401">
@@ -5639,10 +5639,10 @@
         </is>
       </c>
       <c r="B401" t="n">
-        <v>90</v>
+        <v>145</v>
       </c>
       <c r="C401" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="402">
@@ -5652,10 +5652,10 @@
         </is>
       </c>
       <c r="B402" t="n">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C402" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="403">
@@ -5665,10 +5665,10 @@
         </is>
       </c>
       <c r="B403" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C403" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
     </row>
     <row r="404">
@@ -5678,10 +5678,10 @@
         </is>
       </c>
       <c r="B404" t="n">
-        <v>93</v>
+        <v>142</v>
       </c>
       <c r="C404" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="405">
@@ -5691,10 +5691,10 @@
         </is>
       </c>
       <c r="B405" t="n">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="C405" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="406">
@@ -5704,10 +5704,10 @@
         </is>
       </c>
       <c r="B406" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="C406" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="407">
@@ -5720,7 +5720,7 @@
         <v>127</v>
       </c>
       <c r="C407" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="408">
@@ -5730,10 +5730,10 @@
         </is>
       </c>
       <c r="B408" t="n">
-        <v>114</v>
+        <v>140</v>
       </c>
       <c r="C408" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="409">
@@ -5743,10 +5743,10 @@
         </is>
       </c>
       <c r="B409" t="n">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="C409" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
     </row>
     <row r="410">
@@ -5756,10 +5756,10 @@
         </is>
       </c>
       <c r="B410" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C410" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="411">
@@ -5769,10 +5769,10 @@
         </is>
       </c>
       <c r="B411" t="n">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C411" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="412">
@@ -5782,10 +5782,10 @@
         </is>
       </c>
       <c r="B412" t="n">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C412" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="413">
@@ -5795,10 +5795,10 @@
         </is>
       </c>
       <c r="B413" t="n">
-        <v>101</v>
+        <v>136</v>
       </c>
       <c r="C413" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="414">
@@ -5808,10 +5808,10 @@
         </is>
       </c>
       <c r="B414" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C414" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="415">
@@ -5821,10 +5821,10 @@
         </is>
       </c>
       <c r="B415" t="n">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C415" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="416">
@@ -5834,7 +5834,7 @@
         </is>
       </c>
       <c r="B416" t="n">
-        <v>142</v>
+        <v>116</v>
       </c>
       <c r="C416" t="n">
         <v>14</v>
@@ -5847,10 +5847,10 @@
         </is>
       </c>
       <c r="B417" t="n">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C417" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
     </row>
     <row r="418">
@@ -5860,10 +5860,10 @@
         </is>
       </c>
       <c r="B418" t="n">
-        <v>67</v>
+        <v>123</v>
       </c>
       <c r="C418" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="419">
@@ -5873,10 +5873,10 @@
         </is>
       </c>
       <c r="B419" t="n">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="C419" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="420">
@@ -5886,10 +5886,10 @@
         </is>
       </c>
       <c r="B420" t="n">
-        <v>94</v>
+        <v>128</v>
       </c>
       <c r="C420" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="421">
@@ -5899,10 +5899,10 @@
         </is>
       </c>
       <c r="B421" t="n">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C421" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="422">
@@ -5912,10 +5912,10 @@
         </is>
       </c>
       <c r="B422" t="n">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C422" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="423">
@@ -5925,10 +5925,10 @@
         </is>
       </c>
       <c r="B423" t="n">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="C423" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
     </row>
     <row r="424">
@@ -5938,10 +5938,10 @@
         </is>
       </c>
       <c r="B424" t="n">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="C424" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="425">
@@ -5951,10 +5951,10 @@
         </is>
       </c>
       <c r="B425" t="n">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="C425" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="426">
@@ -5964,10 +5964,10 @@
         </is>
       </c>
       <c r="B426" t="n">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C426" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="427">
@@ -5977,10 +5977,10 @@
         </is>
       </c>
       <c r="B427" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C427" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="428">
@@ -5990,10 +5990,10 @@
         </is>
       </c>
       <c r="B428" t="n">
-        <v>109</v>
+        <v>130</v>
       </c>
       <c r="C428" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="429">
@@ -6003,10 +6003,10 @@
         </is>
       </c>
       <c r="B429" t="n">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C429" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
     </row>
     <row r="430">
@@ -6016,10 +6016,10 @@
         </is>
       </c>
       <c r="B430" t="n">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="C430" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="431">
@@ -6029,10 +6029,10 @@
         </is>
       </c>
       <c r="B431" t="n">
-        <v>84</v>
+        <v>124</v>
       </c>
       <c r="C431" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
     </row>
     <row r="432">
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="B432" t="n">
-        <v>97</v>
+        <v>130</v>
       </c>
       <c r="C432" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
     </row>
     <row r="433">
@@ -6055,10 +6055,10 @@
         </is>
       </c>
       <c r="B433" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C433" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="434">
@@ -6068,10 +6068,10 @@
         </is>
       </c>
       <c r="B434" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C434" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="435">
@@ -6081,10 +6081,10 @@
         </is>
       </c>
       <c r="B435" t="n">
-        <v>76</v>
+        <v>127</v>
       </c>
       <c r="C435" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="436">
@@ -6094,10 +6094,10 @@
         </is>
       </c>
       <c r="B436" t="n">
-        <v>84</v>
+        <v>129</v>
       </c>
       <c r="C436" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="437">
@@ -6107,10 +6107,10 @@
         </is>
       </c>
       <c r="B437" t="n">
-        <v>95</v>
+        <v>122</v>
       </c>
       <c r="C437" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="438">
@@ -6120,10 +6120,10 @@
         </is>
       </c>
       <c r="B438" t="n">
-        <v>83</v>
+        <v>124</v>
       </c>
       <c r="C438" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="439">
@@ -6133,10 +6133,10 @@
         </is>
       </c>
       <c r="B439" t="n">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="C439" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="440">
@@ -6146,10 +6146,10 @@
         </is>
       </c>
       <c r="B440" t="n">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C440" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="441">
@@ -6159,10 +6159,10 @@
         </is>
       </c>
       <c r="B441" t="n">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="C441" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="442">
@@ -6172,10 +6172,10 @@
         </is>
       </c>
       <c r="B442" t="n">
-        <v>97</v>
+        <v>130</v>
       </c>
       <c r="C442" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
     </row>
     <row r="443">
@@ -6185,10 +6185,10 @@
         </is>
       </c>
       <c r="B443" t="n">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="C443" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="444">
@@ -6198,10 +6198,10 @@
         </is>
       </c>
       <c r="B444" t="n">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C444" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
     </row>
     <row r="445">
@@ -6211,10 +6211,10 @@
         </is>
       </c>
       <c r="B445" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C445" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="446">
@@ -6224,7 +6224,7 @@
         </is>
       </c>
       <c r="B446" t="n">
-        <v>105</v>
+        <v>139</v>
       </c>
       <c r="C446" t="n">
         <v>9</v>
@@ -6237,10 +6237,10 @@
         </is>
       </c>
       <c r="B447" t="n">
-        <v>162</v>
+        <v>91</v>
       </c>
       <c r="C447" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
     </row>
     <row r="448">
@@ -6250,10 +6250,10 @@
         </is>
       </c>
       <c r="B448" t="n">
-        <v>132</v>
+        <v>114</v>
       </c>
       <c r="C448" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="449">
@@ -6263,10 +6263,10 @@
         </is>
       </c>
       <c r="B449" t="n">
-        <v>97</v>
+        <v>123</v>
       </c>
       <c r="C449" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
     <row r="450">
@@ -6276,10 +6276,10 @@
         </is>
       </c>
       <c r="B450" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C450" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
     </row>
     <row r="451">
@@ -6289,10 +6289,10 @@
         </is>
       </c>
       <c r="B451" t="n">
-        <v>85</v>
+        <v>130</v>
       </c>
       <c r="C451" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
     </row>
     <row r="452">
@@ -6302,10 +6302,10 @@
         </is>
       </c>
       <c r="B452" t="n">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="C452" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="453">
@@ -6315,10 +6315,10 @@
         </is>
       </c>
       <c r="B453" t="n">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C453" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="454">
@@ -6328,10 +6328,10 @@
         </is>
       </c>
       <c r="B454" t="n">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="C454" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
     </row>
     <row r="455">
@@ -6341,10 +6341,10 @@
         </is>
       </c>
       <c r="B455" t="n">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C455" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
     </row>
     <row r="456">
@@ -6354,10 +6354,10 @@
         </is>
       </c>
       <c r="B456" t="n">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="C456" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="457">
@@ -6367,10 +6367,10 @@
         </is>
       </c>
       <c r="B457" t="n">
-        <v>102</v>
+        <v>152</v>
       </c>
       <c r="C457" t="n">
-        <v>31</v>
+        <v>9</v>
       </c>
     </row>
     <row r="458">
@@ -6380,10 +6380,10 @@
         </is>
       </c>
       <c r="B458" t="n">
-        <v>82</v>
+        <v>141</v>
       </c>
       <c r="C458" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="459">
@@ -6393,10 +6393,10 @@
         </is>
       </c>
       <c r="B459" t="n">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="C459" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="460">
@@ -6406,10 +6406,10 @@
         </is>
       </c>
       <c r="B460" t="n">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="C460" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
     </row>
     <row r="461">
@@ -6419,10 +6419,10 @@
         </is>
       </c>
       <c r="B461" t="n">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="C461" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="462">
@@ -6432,10 +6432,10 @@
         </is>
       </c>
       <c r="B462" t="n">
-        <v>105</v>
+        <v>140</v>
       </c>
       <c r="C462" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="463">
@@ -6445,10 +6445,10 @@
         </is>
       </c>
       <c r="B463" t="n">
-        <v>162</v>
+        <v>127</v>
       </c>
       <c r="C463" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="464">
@@ -6458,10 +6458,10 @@
         </is>
       </c>
       <c r="B464" t="n">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="C464" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="465">
@@ -6471,10 +6471,10 @@
         </is>
       </c>
       <c r="B465" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C465" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
     </row>
     <row r="466">
@@ -6484,10 +6484,10 @@
         </is>
       </c>
       <c r="B466" t="n">
-        <v>103</v>
+        <v>124</v>
       </c>
       <c r="C466" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="467">
@@ -6497,10 +6497,10 @@
         </is>
       </c>
       <c r="B467" t="n">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="C467" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="468">
@@ -6510,10 +6510,10 @@
         </is>
       </c>
       <c r="B468" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C468" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="469">
@@ -6523,10 +6523,10 @@
         </is>
       </c>
       <c r="B469" t="n">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="C469" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="470">
@@ -6536,10 +6536,10 @@
         </is>
       </c>
       <c r="B470" t="n">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="C470" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="471">
@@ -6549,10 +6549,10 @@
         </is>
       </c>
       <c r="B471" t="n">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="C471" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
     </row>
     <row r="472">
@@ -6562,10 +6562,10 @@
         </is>
       </c>
       <c r="B472" t="n">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="C472" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
     </row>
     <row r="473">
@@ -6575,10 +6575,10 @@
         </is>
       </c>
       <c r="B473" t="n">
-        <v>99</v>
+        <v>122</v>
       </c>
       <c r="C473" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="474">
@@ -6588,10 +6588,10 @@
         </is>
       </c>
       <c r="B474" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C474" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="475">
@@ -6601,10 +6601,10 @@
         </is>
       </c>
       <c r="B475" t="n">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="C475" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="476">
@@ -6614,10 +6614,10 @@
         </is>
       </c>
       <c r="B476" t="n">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="C476" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
     </row>
     <row r="477">
@@ -6627,10 +6627,10 @@
         </is>
       </c>
       <c r="B477" t="n">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="C477" t="n">
-        <v>33</v>
+        <v>9</v>
       </c>
     </row>
     <row r="478">
@@ -6640,10 +6640,10 @@
         </is>
       </c>
       <c r="B478" t="n">
-        <v>74</v>
+        <v>123</v>
       </c>
       <c r="C478" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="479">
@@ -6653,10 +6653,10 @@
         </is>
       </c>
       <c r="B479" t="n">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="C479" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="480">
@@ -6666,10 +6666,10 @@
         </is>
       </c>
       <c r="B480" t="n">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="C480" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
     </row>
     <row r="481">
@@ -6679,10 +6679,10 @@
         </is>
       </c>
       <c r="B481" t="n">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="C481" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
     </row>
     <row r="482">
@@ -6692,10 +6692,10 @@
         </is>
       </c>
       <c r="B482" t="n">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="C482" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="483">
@@ -6705,10 +6705,10 @@
         </is>
       </c>
       <c r="B483" t="n">
-        <v>98</v>
+        <v>138</v>
       </c>
       <c r="C483" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="484">
@@ -6718,10 +6718,10 @@
         </is>
       </c>
       <c r="B484" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C484" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="485">
@@ -6731,10 +6731,10 @@
         </is>
       </c>
       <c r="B485" t="n">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="C485" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="486">
@@ -6744,10 +6744,10 @@
         </is>
       </c>
       <c r="B486" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="C486" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="487">
@@ -6757,10 +6757,10 @@
         </is>
       </c>
       <c r="B487" t="n">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="C487" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="488">
@@ -6770,10 +6770,10 @@
         </is>
       </c>
       <c r="B488" t="n">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="C488" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="489">
@@ -6783,10 +6783,10 @@
         </is>
       </c>
       <c r="B489" t="n">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C489" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="490">
@@ -6796,10 +6796,10 @@
         </is>
       </c>
       <c r="B490" t="n">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="C490" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="491">
@@ -6809,10 +6809,10 @@
         </is>
       </c>
       <c r="B491" t="n">
-        <v>109</v>
+        <v>136</v>
       </c>
       <c r="C491" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
     </row>
     <row r="492">
@@ -6822,10 +6822,10 @@
         </is>
       </c>
       <c r="B492" t="n">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="C492" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="493">
@@ -6835,10 +6835,10 @@
         </is>
       </c>
       <c r="B493" t="n">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C493" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
     </row>
     <row r="494">
@@ -6848,10 +6848,10 @@
         </is>
       </c>
       <c r="B494" t="n">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="C494" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="495">
@@ -6861,10 +6861,10 @@
         </is>
       </c>
       <c r="B495" t="n">
-        <v>107</v>
+        <v>133</v>
       </c>
       <c r="C495" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="496">
@@ -6874,10 +6874,10 @@
         </is>
       </c>
       <c r="B496" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C496" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
     </row>
     <row r="497">
@@ -6887,10 +6887,10 @@
         </is>
       </c>
       <c r="B497" t="n">
-        <v>101</v>
+        <v>129</v>
       </c>
       <c r="C497" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
     </row>
     <row r="498">
@@ -6900,10 +6900,10 @@
         </is>
       </c>
       <c r="B498" t="n">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="C498" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="499">
@@ -6913,10 +6913,10 @@
         </is>
       </c>
       <c r="B499" t="n">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="C499" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="500">
@@ -6926,10 +6926,10 @@
         </is>
       </c>
       <c r="B500" t="n">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C500" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="501">
@@ -6939,10 +6939,10 @@
         </is>
       </c>
       <c r="B501" t="n">
-        <v>83</v>
+        <v>109</v>
       </c>
       <c r="C501" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="502">
@@ -6952,10 +6952,10 @@
         </is>
       </c>
       <c r="B502" t="n">
-        <v>86</v>
+        <v>112</v>
       </c>
       <c r="C502" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
     <row r="503">
@@ -6965,10 +6965,10 @@
         </is>
       </c>
       <c r="B503" t="n">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C503" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
     </row>
     <row r="504">
@@ -6978,10 +6978,10 @@
         </is>
       </c>
       <c r="B504" t="n">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="C504" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="505">
@@ -6991,10 +6991,10 @@
         </is>
       </c>
       <c r="B505" t="n">
-        <v>83</v>
+        <v>126</v>
       </c>
       <c r="C505" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="506">
@@ -7004,10 +7004,10 @@
         </is>
       </c>
       <c r="B506" t="n">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="C506" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="507">
@@ -7017,10 +7017,10 @@
         </is>
       </c>
       <c r="B507" t="n">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="C507" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="508">
@@ -7030,10 +7030,10 @@
         </is>
       </c>
       <c r="B508" t="n">
-        <v>75</v>
+        <v>145</v>
       </c>
       <c r="C508" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
     </row>
     <row r="509">
@@ -7043,10 +7043,10 @@
         </is>
       </c>
       <c r="B509" t="n">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="C509" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="510">
@@ -7056,10 +7056,10 @@
         </is>
       </c>
       <c r="B510" t="n">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="C510" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="511">
@@ -7069,10 +7069,10 @@
         </is>
       </c>
       <c r="B511" t="n">
-        <v>75</v>
+        <v>138</v>
       </c>
       <c r="C511" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
     </row>
     <row r="512">
@@ -7082,10 +7082,10 @@
         </is>
       </c>
       <c r="B512" t="n">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="C512" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="513">
@@ -7095,10 +7095,10 @@
         </is>
       </c>
       <c r="B513" t="n">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="C513" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
     </row>
     <row r="514">
@@ -7108,10 +7108,10 @@
         </is>
       </c>
       <c r="B514" t="n">
-        <v>112</v>
+        <v>143</v>
       </c>
       <c r="C514" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="515">
@@ -7121,7 +7121,7 @@
         </is>
       </c>
       <c r="B515" t="n">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C515" t="n">
         <v>23</v>
@@ -7134,10 +7134,10 @@
         </is>
       </c>
       <c r="B516" t="n">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="C516" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="517">
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="B517" t="n">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="C517" t="n">
         <v>8</v>
@@ -7160,10 +7160,10 @@
         </is>
       </c>
       <c r="B518" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C518" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="519">
@@ -7173,10 +7173,10 @@
         </is>
       </c>
       <c r="B519" t="n">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C519" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="520">
@@ -7186,10 +7186,10 @@
         </is>
       </c>
       <c r="B520" t="n">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="C520" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="521">
@@ -7199,10 +7199,10 @@
         </is>
       </c>
       <c r="B521" t="n">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="C521" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
     </row>
     <row r="522">
@@ -7212,10 +7212,10 @@
         </is>
       </c>
       <c r="B522" t="n">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="C522" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="523">
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="B523" t="n">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="C523" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="524">
@@ -7238,10 +7238,10 @@
         </is>
       </c>
       <c r="B524" t="n">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="C524" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
     </row>
     <row r="525">
@@ -7251,10 +7251,10 @@
         </is>
       </c>
       <c r="B525" t="n">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="C525" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="526">
@@ -7264,10 +7264,10 @@
         </is>
       </c>
       <c r="B526" t="n">
-        <v>172</v>
+        <v>138</v>
       </c>
       <c r="C526" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="527">
@@ -7277,10 +7277,10 @@
         </is>
       </c>
       <c r="B527" t="n">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="C527" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="528">
@@ -7290,10 +7290,10 @@
         </is>
       </c>
       <c r="B528" t="n">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="C528" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="529">
@@ -7303,7 +7303,7 @@
         </is>
       </c>
       <c r="B529" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C529" t="n">
         <v>19</v>
@@ -7316,10 +7316,10 @@
         </is>
       </c>
       <c r="B530" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C530" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="531">
@@ -7329,10 +7329,10 @@
         </is>
       </c>
       <c r="B531" t="n">
-        <v>114</v>
+        <v>146</v>
       </c>
       <c r="C531" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="532">
@@ -7342,10 +7342,10 @@
         </is>
       </c>
       <c r="B532" t="n">
-        <v>110</v>
+        <v>146</v>
       </c>
       <c r="C532" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
     </row>
     <row r="533">
@@ -7355,7 +7355,7 @@
         </is>
       </c>
       <c r="B533" t="n">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="C533" t="n">
         <v>15</v>
@@ -7368,10 +7368,10 @@
         </is>
       </c>
       <c r="B534" t="n">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="C534" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="535">
@@ -7381,10 +7381,10 @@
         </is>
       </c>
       <c r="B535" t="n">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="C535" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="536">
@@ -7394,10 +7394,10 @@
         </is>
       </c>
       <c r="B536" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C536" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="537">
@@ -7407,10 +7407,10 @@
         </is>
       </c>
       <c r="B537" t="n">
-        <v>106</v>
+        <v>141</v>
       </c>
       <c r="C537" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="538">
@@ -7420,7 +7420,7 @@
         </is>
       </c>
       <c r="B538" t="n">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C538" t="n">
         <v>15</v>
@@ -7433,10 +7433,10 @@
         </is>
       </c>
       <c r="B539" t="n">
-        <v>98</v>
+        <v>129</v>
       </c>
       <c r="C539" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="540">
@@ -7446,10 +7446,10 @@
         </is>
       </c>
       <c r="B540" t="n">
-        <v>96</v>
+        <v>123</v>
       </c>
       <c r="C540" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="541">
@@ -7459,10 +7459,10 @@
         </is>
       </c>
       <c r="B541" t="n">
-        <v>113</v>
+        <v>151</v>
       </c>
       <c r="C541" t="n">
-        <v>31</v>
+        <v>12</v>
       </c>
     </row>
     <row r="542">
@@ -7472,10 +7472,10 @@
         </is>
       </c>
       <c r="B542" t="n">
-        <v>111</v>
+        <v>152</v>
       </c>
       <c r="C542" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="543">
@@ -7485,10 +7485,10 @@
         </is>
       </c>
       <c r="B543" t="n">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C543" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="544">
@@ -7498,10 +7498,10 @@
         </is>
       </c>
       <c r="B544" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C544" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
     </row>
     <row r="545">
@@ -7511,10 +7511,10 @@
         </is>
       </c>
       <c r="B545" t="n">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="C545" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="546">
@@ -7524,10 +7524,10 @@
         </is>
       </c>
       <c r="B546" t="n">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="C546" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="547">
@@ -7537,10 +7537,10 @@
         </is>
       </c>
       <c r="B547" t="n">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="C547" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
     </row>
     <row r="548">
@@ -7550,10 +7550,10 @@
         </is>
       </c>
       <c r="B548" t="n">
-        <v>107</v>
+        <v>147</v>
       </c>
       <c r="C548" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="549">
@@ -7563,10 +7563,10 @@
         </is>
       </c>
       <c r="B549" t="n">
-        <v>93</v>
+        <v>152</v>
       </c>
       <c r="C549" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="550">
@@ -7576,10 +7576,10 @@
         </is>
       </c>
       <c r="B550" t="n">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="C550" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="551">
@@ -7589,10 +7589,10 @@
         </is>
       </c>
       <c r="B551" t="n">
-        <v>105</v>
+        <v>134</v>
       </c>
       <c r="C551" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
     </row>
     <row r="552">
@@ -7602,10 +7602,10 @@
         </is>
       </c>
       <c r="B552" t="n">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="C552" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="553">
@@ -7615,10 +7615,10 @@
         </is>
       </c>
       <c r="B553" t="n">
-        <v>87</v>
+        <v>128</v>
       </c>
       <c r="C553" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="554">
@@ -7628,10 +7628,10 @@
         </is>
       </c>
       <c r="B554" t="n">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="C554" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="555">
@@ -7641,10 +7641,10 @@
         </is>
       </c>
       <c r="B555" t="n">
-        <v>102</v>
+        <v>145</v>
       </c>
       <c r="C555" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="556">
@@ -7654,10 +7654,10 @@
         </is>
       </c>
       <c r="B556" t="n">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="C556" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
     </row>
     <row r="557">
@@ -7667,10 +7667,10 @@
         </is>
       </c>
       <c r="B557" t="n">
-        <v>80</v>
+        <v>132</v>
       </c>
       <c r="C557" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="558">
@@ -7680,10 +7680,10 @@
         </is>
       </c>
       <c r="B558" t="n">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="C558" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="559">
@@ -7693,10 +7693,10 @@
         </is>
       </c>
       <c r="B559" t="n">
-        <v>124</v>
+        <v>84</v>
       </c>
       <c r="C559" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
     </row>
     <row r="560">
@@ -7706,10 +7706,10 @@
         </is>
       </c>
       <c r="B560" t="n">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="C560" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="561">
@@ -7719,10 +7719,10 @@
         </is>
       </c>
       <c r="B561" t="n">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="C561" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="562">
@@ -7732,10 +7732,10 @@
         </is>
       </c>
       <c r="B562" t="n">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="C562" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="563">
@@ -7745,10 +7745,10 @@
         </is>
       </c>
       <c r="B563" t="n">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C563" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="564">
@@ -7758,10 +7758,10 @@
         </is>
       </c>
       <c r="B564" t="n">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="C564" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="565">
@@ -7771,10 +7771,10 @@
         </is>
       </c>
       <c r="B565" t="n">
-        <v>103</v>
+        <v>134</v>
       </c>
       <c r="C565" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
     </row>
     <row r="566">
@@ -7784,10 +7784,10 @@
         </is>
       </c>
       <c r="B566" t="n">
-        <v>81</v>
+        <v>152</v>
       </c>
       <c r="C566" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
     </row>
     <row r="567">
@@ -7797,10 +7797,10 @@
         </is>
       </c>
       <c r="B567" t="n">
-        <v>121</v>
+        <v>142</v>
       </c>
       <c r="C567" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="568">
@@ -7810,10 +7810,10 @@
         </is>
       </c>
       <c r="B568" t="n">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c r="C568" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="569">
@@ -7823,10 +7823,10 @@
         </is>
       </c>
       <c r="B569" t="n">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="C569" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="570">
@@ -7836,10 +7836,10 @@
         </is>
       </c>
       <c r="B570" t="n">
-        <v>62</v>
+        <v>134</v>
       </c>
       <c r="C570" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="571">
@@ -7849,10 +7849,10 @@
         </is>
       </c>
       <c r="B571" t="n">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="C571" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="572">
@@ -7862,10 +7862,10 @@
         </is>
       </c>
       <c r="B572" t="n">
-        <v>98</v>
+        <v>150</v>
       </c>
       <c r="C572" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
     </row>
     <row r="573">
@@ -7875,10 +7875,10 @@
         </is>
       </c>
       <c r="B573" t="n">
-        <v>121</v>
+        <v>144</v>
       </c>
       <c r="C573" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="574">
@@ -7888,10 +7888,10 @@
         </is>
       </c>
       <c r="B574" t="n">
-        <v>118</v>
+        <v>141</v>
       </c>
       <c r="C574" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="575">
@@ -7901,10 +7901,10 @@
         </is>
       </c>
       <c r="B575" t="n">
-        <v>102</v>
+        <v>134</v>
       </c>
       <c r="C575" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="576">
@@ -7914,10 +7914,10 @@
         </is>
       </c>
       <c r="B576" t="n">
-        <v>96</v>
+        <v>151</v>
       </c>
       <c r="C576" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="577">
@@ -7927,10 +7927,10 @@
         </is>
       </c>
       <c r="B577" t="n">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="C577" t="n">
-        <v>31</v>
+        <v>12</v>
       </c>
     </row>
     <row r="578">
@@ -7940,10 +7940,10 @@
         </is>
       </c>
       <c r="B578" t="n">
-        <v>109</v>
+        <v>144</v>
       </c>
       <c r="C578" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="579">
@@ -7953,10 +7953,10 @@
         </is>
       </c>
       <c r="B579" t="n">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="C579" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="580">
@@ -7966,10 +7966,10 @@
         </is>
       </c>
       <c r="B580" t="n">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="C580" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
     </row>
     <row r="581">
@@ -7979,10 +7979,10 @@
         </is>
       </c>
       <c r="B581" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C581" t="n">
-        <v>37</v>
+        <v>17</v>
       </c>
     </row>
     <row r="582">
@@ -7992,10 +7992,10 @@
         </is>
       </c>
       <c r="B582" t="n">
-        <v>121</v>
+        <v>142</v>
       </c>
       <c r="C582" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="583">
@@ -8005,10 +8005,10 @@
         </is>
       </c>
       <c r="B583" t="n">
-        <v>112</v>
+        <v>144</v>
       </c>
       <c r="C583" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
     </row>
     <row r="584">
@@ -8018,10 +8018,10 @@
         </is>
       </c>
       <c r="B584" t="n">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="C584" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="585">
@@ -8031,10 +8031,10 @@
         </is>
       </c>
       <c r="B585" t="n">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="C585" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="586">
@@ -8044,10 +8044,10 @@
         </is>
       </c>
       <c r="B586" t="n">
-        <v>93</v>
+        <v>119</v>
       </c>
       <c r="C586" t="n">
-        <v>31</v>
+        <v>9</v>
       </c>
     </row>
     <row r="587">
@@ -8057,10 +8057,10 @@
         </is>
       </c>
       <c r="B587" t="n">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="C587" t="n">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="588">
@@ -8070,10 +8070,10 @@
         </is>
       </c>
       <c r="B588" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C588" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="589">
@@ -8083,10 +8083,10 @@
         </is>
       </c>
       <c r="B589" t="n">
-        <v>101</v>
+        <v>132</v>
       </c>
       <c r="C589" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
     </row>
     <row r="590">
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="B590" t="n">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="C590" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
     </row>
     <row r="591">
@@ -8109,10 +8109,10 @@
         </is>
       </c>
       <c r="B591" t="n">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C591" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="592">
@@ -8122,10 +8122,10 @@
         </is>
       </c>
       <c r="B592" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="C592" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="593">
@@ -8135,10 +8135,10 @@
         </is>
       </c>
       <c r="B593" t="n">
-        <v>96</v>
+        <v>128</v>
       </c>
       <c r="C593" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
     </row>
     <row r="594">
@@ -8148,10 +8148,10 @@
         </is>
       </c>
       <c r="B594" t="n">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="C594" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="595">
@@ -8161,10 +8161,10 @@
         </is>
       </c>
       <c r="B595" t="n">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="C595" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="596">
@@ -8174,10 +8174,10 @@
         </is>
       </c>
       <c r="B596" t="n">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="C596" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="597">
@@ -8187,10 +8187,10 @@
         </is>
       </c>
       <c r="B597" t="n">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C597" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
     </row>
     <row r="598">
@@ -8200,10 +8200,10 @@
         </is>
       </c>
       <c r="B598" t="n">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="C598" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
     </row>
     <row r="599">
@@ -8213,10 +8213,10 @@
         </is>
       </c>
       <c r="B599" t="n">
-        <v>106</v>
+        <v>129</v>
       </c>
       <c r="C599" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="600">
@@ -8226,10 +8226,10 @@
         </is>
       </c>
       <c r="B600" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C600" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="601">
@@ -8239,10 +8239,10 @@
         </is>
       </c>
       <c r="B601" t="n">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="C601" t="n">
-        <v>37</v>
+        <v>2</v>
       </c>
     </row>
     <row r="602">
@@ -8252,10 +8252,10 @@
         </is>
       </c>
       <c r="B602" t="n">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="C602" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
     </row>
     <row r="603">
@@ -8265,10 +8265,10 @@
         </is>
       </c>
       <c r="B603" t="n">
-        <v>112</v>
+        <v>136</v>
       </c>
       <c r="C603" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
     </row>
     <row r="604">
@@ -8278,7 +8278,7 @@
         </is>
       </c>
       <c r="B604" t="n">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="C604" t="n">
         <v>10</v>
@@ -8291,10 +8291,10 @@
         </is>
       </c>
       <c r="B605" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C605" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="606">
@@ -8304,10 +8304,10 @@
         </is>
       </c>
       <c r="B606" t="n">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C606" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="607">
@@ -8317,10 +8317,10 @@
         </is>
       </c>
       <c r="B607" t="n">
-        <v>151</v>
+        <v>118</v>
       </c>
       <c r="C607" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="608">
@@ -8330,10 +8330,10 @@
         </is>
       </c>
       <c r="B608" t="n">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="C608" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="609">
@@ -8343,10 +8343,10 @@
         </is>
       </c>
       <c r="B609" t="n">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="C609" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="610">
@@ -8356,10 +8356,10 @@
         </is>
       </c>
       <c r="B610" t="n">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="C610" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="611">
@@ -8369,10 +8369,10 @@
         </is>
       </c>
       <c r="B611" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="C611" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="612">
@@ -8382,10 +8382,10 @@
         </is>
       </c>
       <c r="B612" t="n">
-        <v>102</v>
+        <v>125</v>
       </c>
       <c r="C612" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="613">
@@ -8395,10 +8395,10 @@
         </is>
       </c>
       <c r="B613" t="n">
-        <v>105</v>
+        <v>140</v>
       </c>
       <c r="C613" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
     </row>
     <row r="614">
@@ -8408,10 +8408,10 @@
         </is>
       </c>
       <c r="B614" t="n">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="C614" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="615">
@@ -8421,10 +8421,10 @@
         </is>
       </c>
       <c r="B615" t="n">
-        <v>128</v>
+        <v>156</v>
       </c>
       <c r="C615" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="616">
@@ -8434,7 +8434,7 @@
         </is>
       </c>
       <c r="B616" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C616" t="n">
         <v>24</v>
@@ -8447,10 +8447,10 @@
         </is>
       </c>
       <c r="B617" t="n">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="C617" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
     </row>
     <row r="618">
@@ -8460,10 +8460,10 @@
         </is>
       </c>
       <c r="B618" t="n">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="C618" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
     </row>
     <row r="619">
@@ -8473,10 +8473,10 @@
         </is>
       </c>
       <c r="B619" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C619" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="620">
@@ -8486,10 +8486,10 @@
         </is>
       </c>
       <c r="B620" t="n">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="C620" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="621">
@@ -8499,10 +8499,10 @@
         </is>
       </c>
       <c r="B621" t="n">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="C621" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="622">
@@ -8512,10 +8512,10 @@
         </is>
       </c>
       <c r="B622" t="n">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="C622" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
     </row>
     <row r="623">
@@ -8525,10 +8525,10 @@
         </is>
       </c>
       <c r="B623" t="n">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C623" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="624">
@@ -8538,10 +8538,10 @@
         </is>
       </c>
       <c r="B624" t="n">
-        <v>95</v>
+        <v>114</v>
       </c>
       <c r="C624" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="625">
@@ -8551,10 +8551,10 @@
         </is>
       </c>
       <c r="B625" t="n">
-        <v>153</v>
+        <v>130</v>
       </c>
       <c r="C625" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="626">
@@ -8564,10 +8564,10 @@
         </is>
       </c>
       <c r="B626" t="n">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="C626" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="627">
@@ -8577,10 +8577,10 @@
         </is>
       </c>
       <c r="B627" t="n">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="C627" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="628">
@@ -8590,10 +8590,10 @@
         </is>
       </c>
       <c r="B628" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C628" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="629">
@@ -8603,10 +8603,10 @@
         </is>
       </c>
       <c r="B629" t="n">
-        <v>93</v>
+        <v>140</v>
       </c>
       <c r="C629" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="630">
@@ -8616,1544 +8616,10 @@
         </is>
       </c>
       <c r="B630" t="n">
-        <v>138</v>
+        <v>178</v>
       </c>
       <c r="C630" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="631">
-      <c r="A631" t="inlineStr">
-        <is>
-          <t>F8_0703_630</t>
-        </is>
-      </c>
-      <c r="B631" t="n">
-        <v>126</v>
-      </c>
-      <c r="C631" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="632">
-      <c r="A632" t="inlineStr">
-        <is>
-          <t>F8_0703_631</t>
-        </is>
-      </c>
-      <c r="B632" t="n">
-        <v>112</v>
-      </c>
-      <c r="C632" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="633">
-      <c r="A633" t="inlineStr">
-        <is>
-          <t>F8_0703_632</t>
-        </is>
-      </c>
-      <c r="B633" t="n">
-        <v>130</v>
-      </c>
-      <c r="C633" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="634">
-      <c r="A634" t="inlineStr">
-        <is>
-          <t>F8_0703_633</t>
-        </is>
-      </c>
-      <c r="B634" t="n">
-        <v>112</v>
-      </c>
-      <c r="C634" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="635">
-      <c r="A635" t="inlineStr">
-        <is>
-          <t>F8_0703_634</t>
-        </is>
-      </c>
-      <c r="B635" t="n">
-        <v>112</v>
-      </c>
-      <c r="C635" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="636">
-      <c r="A636" t="inlineStr">
-        <is>
-          <t>F8_0703_635</t>
-        </is>
-      </c>
-      <c r="B636" t="n">
-        <v>168</v>
-      </c>
-      <c r="C636" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="637">
-      <c r="A637" t="inlineStr">
-        <is>
-          <t>F8_0703_636</t>
-        </is>
-      </c>
-      <c r="B637" t="n">
-        <v>124</v>
-      </c>
-      <c r="C637" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="638">
-      <c r="A638" t="inlineStr">
-        <is>
-          <t>F8_0703_637</t>
-        </is>
-      </c>
-      <c r="B638" t="n">
-        <v>149</v>
-      </c>
-      <c r="C638" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="639">
-      <c r="A639" t="inlineStr">
-        <is>
-          <t>F8_0703_638</t>
-        </is>
-      </c>
-      <c r="B639" t="n">
-        <v>149</v>
-      </c>
-      <c r="C639" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="640">
-      <c r="A640" t="inlineStr">
-        <is>
-          <t>F8_0703_639</t>
-        </is>
-      </c>
-      <c r="B640" t="n">
-        <v>115</v>
-      </c>
-      <c r="C640" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="641">
-      <c r="A641" t="inlineStr">
-        <is>
-          <t>F8_0703_640</t>
-        </is>
-      </c>
-      <c r="B641" t="n">
-        <v>63</v>
-      </c>
-      <c r="C641" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="642">
-      <c r="A642" t="inlineStr">
-        <is>
-          <t>F8_0703_641</t>
-        </is>
-      </c>
-      <c r="B642" t="n">
-        <v>109</v>
-      </c>
-      <c r="C642" t="n">
         <v>8</v>
-      </c>
-    </row>
-    <row r="643">
-      <c r="A643" t="inlineStr">
-        <is>
-          <t>F8_0703_642</t>
-        </is>
-      </c>
-      <c r="B643" t="n">
-        <v>134</v>
-      </c>
-      <c r="C643" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="644">
-      <c r="A644" t="inlineStr">
-        <is>
-          <t>F8_0703_643</t>
-        </is>
-      </c>
-      <c r="B644" t="n">
-        <v>103</v>
-      </c>
-      <c r="C644" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="645">
-      <c r="A645" t="inlineStr">
-        <is>
-          <t>F8_0703_644</t>
-        </is>
-      </c>
-      <c r="B645" t="n">
-        <v>103</v>
-      </c>
-      <c r="C645" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="646">
-      <c r="A646" t="inlineStr">
-        <is>
-          <t>F8_0703_645</t>
-        </is>
-      </c>
-      <c r="B646" t="n">
-        <v>113</v>
-      </c>
-      <c r="C646" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="647">
-      <c r="A647" t="inlineStr">
-        <is>
-          <t>F8_0703_646</t>
-        </is>
-      </c>
-      <c r="B647" t="n">
-        <v>115</v>
-      </c>
-      <c r="C647" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="648">
-      <c r="A648" t="inlineStr">
-        <is>
-          <t>F8_0703_647</t>
-        </is>
-      </c>
-      <c r="B648" t="n">
-        <v>125</v>
-      </c>
-      <c r="C648" t="n">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="649">
-      <c r="A649" t="inlineStr">
-        <is>
-          <t>F8_0703_648</t>
-        </is>
-      </c>
-      <c r="B649" t="n">
-        <v>82</v>
-      </c>
-      <c r="C649" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="650">
-      <c r="A650" t="inlineStr">
-        <is>
-          <t>F8_0703_649</t>
-        </is>
-      </c>
-      <c r="B650" t="n">
-        <v>73</v>
-      </c>
-      <c r="C650" t="n">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="651">
-      <c r="A651" t="inlineStr">
-        <is>
-          <t>F8_0703_650</t>
-        </is>
-      </c>
-      <c r="B651" t="n">
-        <v>87</v>
-      </c>
-      <c r="C651" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="652">
-      <c r="A652" t="inlineStr">
-        <is>
-          <t>F8_0703_651</t>
-        </is>
-      </c>
-      <c r="B652" t="n">
-        <v>117</v>
-      </c>
-      <c r="C652" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="653">
-      <c r="A653" t="inlineStr">
-        <is>
-          <t>F8_0703_652</t>
-        </is>
-      </c>
-      <c r="B653" t="n">
-        <v>118</v>
-      </c>
-      <c r="C653" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="654">
-      <c r="A654" t="inlineStr">
-        <is>
-          <t>F8_0703_653</t>
-        </is>
-      </c>
-      <c r="B654" t="n">
-        <v>135</v>
-      </c>
-      <c r="C654" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="655">
-      <c r="A655" t="inlineStr">
-        <is>
-          <t>F8_0703_654</t>
-        </is>
-      </c>
-      <c r="B655" t="n">
-        <v>100</v>
-      </c>
-      <c r="C655" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="656">
-      <c r="A656" t="inlineStr">
-        <is>
-          <t>F8_0703_655</t>
-        </is>
-      </c>
-      <c r="B656" t="n">
-        <v>116</v>
-      </c>
-      <c r="C656" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="657">
-      <c r="A657" t="inlineStr">
-        <is>
-          <t>F8_0703_656</t>
-        </is>
-      </c>
-      <c r="B657" t="n">
-        <v>124</v>
-      </c>
-      <c r="C657" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="658">
-      <c r="A658" t="inlineStr">
-        <is>
-          <t>F8_0703_657</t>
-        </is>
-      </c>
-      <c r="B658" t="n">
-        <v>134</v>
-      </c>
-      <c r="C658" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="659">
-      <c r="A659" t="inlineStr">
-        <is>
-          <t>F8_0703_658</t>
-        </is>
-      </c>
-      <c r="B659" t="n">
-        <v>97</v>
-      </c>
-      <c r="C659" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="660">
-      <c r="A660" t="inlineStr">
-        <is>
-          <t>F8_0703_659</t>
-        </is>
-      </c>
-      <c r="B660" t="n">
-        <v>111</v>
-      </c>
-      <c r="C660" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="661">
-      <c r="A661" t="inlineStr">
-        <is>
-          <t>F8_0703_660</t>
-        </is>
-      </c>
-      <c r="B661" t="n">
-        <v>47</v>
-      </c>
-      <c r="C661" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="662">
-      <c r="A662" t="inlineStr">
-        <is>
-          <t>F8_0703_661</t>
-        </is>
-      </c>
-      <c r="B662" t="n">
-        <v>113</v>
-      </c>
-      <c r="C662" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="663">
-      <c r="A663" t="inlineStr">
-        <is>
-          <t>F8_0703_662</t>
-        </is>
-      </c>
-      <c r="B663" t="n">
-        <v>139</v>
-      </c>
-      <c r="C663" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="664">
-      <c r="A664" t="inlineStr">
-        <is>
-          <t>F8_0703_663</t>
-        </is>
-      </c>
-      <c r="B664" t="n">
-        <v>120</v>
-      </c>
-      <c r="C664" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="665">
-      <c r="A665" t="inlineStr">
-        <is>
-          <t>F8_0703_664</t>
-        </is>
-      </c>
-      <c r="B665" t="n">
-        <v>136</v>
-      </c>
-      <c r="C665" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="666">
-      <c r="A666" t="inlineStr">
-        <is>
-          <t>F8_0703_665</t>
-        </is>
-      </c>
-      <c r="B666" t="n">
-        <v>149</v>
-      </c>
-      <c r="C666" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="667">
-      <c r="A667" t="inlineStr">
-        <is>
-          <t>F8_0703_666</t>
-        </is>
-      </c>
-      <c r="B667" t="n">
-        <v>137</v>
-      </c>
-      <c r="C667" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="668">
-      <c r="A668" t="inlineStr">
-        <is>
-          <t>F8_0703_667</t>
-        </is>
-      </c>
-      <c r="B668" t="n">
-        <v>140</v>
-      </c>
-      <c r="C668" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="669">
-      <c r="A669" t="inlineStr">
-        <is>
-          <t>F8_0703_668</t>
-        </is>
-      </c>
-      <c r="B669" t="n">
-        <v>118</v>
-      </c>
-      <c r="C669" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="670">
-      <c r="A670" t="inlineStr">
-        <is>
-          <t>F8_0703_669</t>
-        </is>
-      </c>
-      <c r="B670" t="n">
-        <v>78</v>
-      </c>
-      <c r="C670" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="671">
-      <c r="A671" t="inlineStr">
-        <is>
-          <t>F8_0703_670</t>
-        </is>
-      </c>
-      <c r="B671" t="n">
-        <v>90</v>
-      </c>
-      <c r="C671" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="672">
-      <c r="A672" t="inlineStr">
-        <is>
-          <t>F8_0703_671</t>
-        </is>
-      </c>
-      <c r="B672" t="n">
-        <v>212</v>
-      </c>
-      <c r="C672" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="673">
-      <c r="A673" t="inlineStr">
-        <is>
-          <t>F8_0703_672</t>
-        </is>
-      </c>
-      <c r="B673" t="n">
-        <v>88</v>
-      </c>
-      <c r="C673" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="674">
-      <c r="A674" t="inlineStr">
-        <is>
-          <t>F8_0703_673</t>
-        </is>
-      </c>
-      <c r="B674" t="n">
-        <v>96</v>
-      </c>
-      <c r="C674" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="675">
-      <c r="A675" t="inlineStr">
-        <is>
-          <t>F8_0703_674</t>
-        </is>
-      </c>
-      <c r="B675" t="n">
-        <v>124</v>
-      </c>
-      <c r="C675" t="n">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="676">
-      <c r="A676" t="inlineStr">
-        <is>
-          <t>F8_0703_675</t>
-        </is>
-      </c>
-      <c r="B676" t="n">
-        <v>129</v>
-      </c>
-      <c r="C676" t="n">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="677">
-      <c r="A677" t="inlineStr">
-        <is>
-          <t>F8_0703_676</t>
-        </is>
-      </c>
-      <c r="B677" t="n">
-        <v>65</v>
-      </c>
-      <c r="C677" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="678">
-      <c r="A678" t="inlineStr">
-        <is>
-          <t>F8_0703_677</t>
-        </is>
-      </c>
-      <c r="B678" t="n">
-        <v>133</v>
-      </c>
-      <c r="C678" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="679">
-      <c r="A679" t="inlineStr">
-        <is>
-          <t>F8_0703_678</t>
-        </is>
-      </c>
-      <c r="B679" t="n">
-        <v>110</v>
-      </c>
-      <c r="C679" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="680">
-      <c r="A680" t="inlineStr">
-        <is>
-          <t>F8_0703_679</t>
-        </is>
-      </c>
-      <c r="B680" t="n">
-        <v>118</v>
-      </c>
-      <c r="C680" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="681">
-      <c r="A681" t="inlineStr">
-        <is>
-          <t>F8_0703_680</t>
-        </is>
-      </c>
-      <c r="B681" t="n">
-        <v>102</v>
-      </c>
-      <c r="C681" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="682">
-      <c r="A682" t="inlineStr">
-        <is>
-          <t>F8_0703_681</t>
-        </is>
-      </c>
-      <c r="B682" t="n">
-        <v>145</v>
-      </c>
-      <c r="C682" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="683">
-      <c r="A683" t="inlineStr">
-        <is>
-          <t>F8_0703_682</t>
-        </is>
-      </c>
-      <c r="B683" t="n">
-        <v>112</v>
-      </c>
-      <c r="C683" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="684">
-      <c r="A684" t="inlineStr">
-        <is>
-          <t>F8_0703_683</t>
-        </is>
-      </c>
-      <c r="B684" t="n">
-        <v>110</v>
-      </c>
-      <c r="C684" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="685">
-      <c r="A685" t="inlineStr">
-        <is>
-          <t>F8_0703_684</t>
-        </is>
-      </c>
-      <c r="B685" t="n">
-        <v>126</v>
-      </c>
-      <c r="C685" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="686">
-      <c r="A686" t="inlineStr">
-        <is>
-          <t>F8_0703_685</t>
-        </is>
-      </c>
-      <c r="B686" t="n">
-        <v>111</v>
-      </c>
-      <c r="C686" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="687">
-      <c r="A687" t="inlineStr">
-        <is>
-          <t>F8_0703_686</t>
-        </is>
-      </c>
-      <c r="B687" t="n">
-        <v>131</v>
-      </c>
-      <c r="C687" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="688">
-      <c r="A688" t="inlineStr">
-        <is>
-          <t>F8_0703_687</t>
-        </is>
-      </c>
-      <c r="B688" t="n">
-        <v>103</v>
-      </c>
-      <c r="C688" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="689">
-      <c r="A689" t="inlineStr">
-        <is>
-          <t>F8_0703_688</t>
-        </is>
-      </c>
-      <c r="B689" t="n">
-        <v>60</v>
-      </c>
-      <c r="C689" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="690">
-      <c r="A690" t="inlineStr">
-        <is>
-          <t>F8_0703_689</t>
-        </is>
-      </c>
-      <c r="B690" t="n">
-        <v>133</v>
-      </c>
-      <c r="C690" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="691">
-      <c r="A691" t="inlineStr">
-        <is>
-          <t>F8_0703_690</t>
-        </is>
-      </c>
-      <c r="B691" t="n">
-        <v>125</v>
-      </c>
-      <c r="C691" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="692">
-      <c r="A692" t="inlineStr">
-        <is>
-          <t>F8_0703_691</t>
-        </is>
-      </c>
-      <c r="B692" t="n">
-        <v>126</v>
-      </c>
-      <c r="C692" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="693">
-      <c r="A693" t="inlineStr">
-        <is>
-          <t>F8_0703_692</t>
-        </is>
-      </c>
-      <c r="B693" t="n">
-        <v>147</v>
-      </c>
-      <c r="C693" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="694">
-      <c r="A694" t="inlineStr">
-        <is>
-          <t>F8_0703_693</t>
-        </is>
-      </c>
-      <c r="B694" t="n">
-        <v>110</v>
-      </c>
-      <c r="C694" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="695">
-      <c r="A695" t="inlineStr">
-        <is>
-          <t>F8_0703_694</t>
-        </is>
-      </c>
-      <c r="B695" t="n">
-        <v>125</v>
-      </c>
-      <c r="C695" t="n">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="696">
-      <c r="A696" t="inlineStr">
-        <is>
-          <t>F8_0703_695</t>
-        </is>
-      </c>
-      <c r="B696" t="n">
-        <v>152</v>
-      </c>
-      <c r="C696" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="697">
-      <c r="A697" t="inlineStr">
-        <is>
-          <t>F8_0703_696</t>
-        </is>
-      </c>
-      <c r="B697" t="n">
-        <v>111</v>
-      </c>
-      <c r="C697" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="698">
-      <c r="A698" t="inlineStr">
-        <is>
-          <t>F8_0703_697</t>
-        </is>
-      </c>
-      <c r="B698" t="n">
-        <v>102</v>
-      </c>
-      <c r="C698" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="699">
-      <c r="A699" t="inlineStr">
-        <is>
-          <t>F8_0703_698</t>
-        </is>
-      </c>
-      <c r="B699" t="n">
-        <v>101</v>
-      </c>
-      <c r="C699" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="700">
-      <c r="A700" t="inlineStr">
-        <is>
-          <t>F8_0703_699</t>
-        </is>
-      </c>
-      <c r="B700" t="n">
-        <v>136</v>
-      </c>
-      <c r="C700" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="701">
-      <c r="A701" t="inlineStr">
-        <is>
-          <t>F8_0703_700</t>
-        </is>
-      </c>
-      <c r="B701" t="n">
-        <v>114</v>
-      </c>
-      <c r="C701" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="702">
-      <c r="A702" t="inlineStr">
-        <is>
-          <t>F8_0703_701</t>
-        </is>
-      </c>
-      <c r="B702" t="n">
-        <v>133</v>
-      </c>
-      <c r="C702" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="703">
-      <c r="A703" t="inlineStr">
-        <is>
-          <t>F8_0703_702</t>
-        </is>
-      </c>
-      <c r="B703" t="n">
-        <v>116</v>
-      </c>
-      <c r="C703" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="704">
-      <c r="A704" t="inlineStr">
-        <is>
-          <t>F8_0703_703</t>
-        </is>
-      </c>
-      <c r="B704" t="n">
-        <v>101</v>
-      </c>
-      <c r="C704" t="n">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="705">
-      <c r="A705" t="inlineStr">
-        <is>
-          <t>F8_0703_704</t>
-        </is>
-      </c>
-      <c r="B705" t="n">
-        <v>120</v>
-      </c>
-      <c r="C705" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="706">
-      <c r="A706" t="inlineStr">
-        <is>
-          <t>F8_0703_705</t>
-        </is>
-      </c>
-      <c r="B706" t="n">
-        <v>156</v>
-      </c>
-      <c r="C706" t="n">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="707">
-      <c r="A707" t="inlineStr">
-        <is>
-          <t>F8_0703_706</t>
-        </is>
-      </c>
-      <c r="B707" t="n">
-        <v>138</v>
-      </c>
-      <c r="C707" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="708">
-      <c r="A708" t="inlineStr">
-        <is>
-          <t>F8_0703_707</t>
-        </is>
-      </c>
-      <c r="B708" t="n">
-        <v>122</v>
-      </c>
-      <c r="C708" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="709">
-      <c r="A709" t="inlineStr">
-        <is>
-          <t>F8_0703_708</t>
-        </is>
-      </c>
-      <c r="B709" t="n">
-        <v>101</v>
-      </c>
-      <c r="C709" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="710">
-      <c r="A710" t="inlineStr">
-        <is>
-          <t>F8_0703_709</t>
-        </is>
-      </c>
-      <c r="B710" t="n">
-        <v>82</v>
-      </c>
-      <c r="C710" t="n">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="711">
-      <c r="A711" t="inlineStr">
-        <is>
-          <t>F8_0703_710</t>
-        </is>
-      </c>
-      <c r="B711" t="n">
-        <v>109</v>
-      </c>
-      <c r="C711" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="712">
-      <c r="A712" t="inlineStr">
-        <is>
-          <t>F8_0703_711</t>
-        </is>
-      </c>
-      <c r="B712" t="n">
-        <v>111</v>
-      </c>
-      <c r="C712" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="713">
-      <c r="A713" t="inlineStr">
-        <is>
-          <t>F8_0703_712</t>
-        </is>
-      </c>
-      <c r="B713" t="n">
-        <v>104</v>
-      </c>
-      <c r="C713" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="714">
-      <c r="A714" t="inlineStr">
-        <is>
-          <t>F8_0703_713</t>
-        </is>
-      </c>
-      <c r="B714" t="n">
-        <v>113</v>
-      </c>
-      <c r="C714" t="n">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="715">
-      <c r="A715" t="inlineStr">
-        <is>
-          <t>F8_0703_714</t>
-        </is>
-      </c>
-      <c r="B715" t="n">
-        <v>112</v>
-      </c>
-      <c r="C715" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="716">
-      <c r="A716" t="inlineStr">
-        <is>
-          <t>F8_0703_715</t>
-        </is>
-      </c>
-      <c r="B716" t="n">
-        <v>107</v>
-      </c>
-      <c r="C716" t="n">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="717">
-      <c r="A717" t="inlineStr">
-        <is>
-          <t>F8_0703_716</t>
-        </is>
-      </c>
-      <c r="B717" t="n">
-        <v>125</v>
-      </c>
-      <c r="C717" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="718">
-      <c r="A718" t="inlineStr">
-        <is>
-          <t>F8_0703_717</t>
-        </is>
-      </c>
-      <c r="B718" t="n">
-        <v>132</v>
-      </c>
-      <c r="C718" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="719">
-      <c r="A719" t="inlineStr">
-        <is>
-          <t>F8_0703_718</t>
-        </is>
-      </c>
-      <c r="B719" t="n">
-        <v>90</v>
-      </c>
-      <c r="C719" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="720">
-      <c r="A720" t="inlineStr">
-        <is>
-          <t>F8_0703_719</t>
-        </is>
-      </c>
-      <c r="B720" t="n">
-        <v>106</v>
-      </c>
-      <c r="C720" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="721">
-      <c r="A721" t="inlineStr">
-        <is>
-          <t>F8_0703_720</t>
-        </is>
-      </c>
-      <c r="B721" t="n">
-        <v>97</v>
-      </c>
-      <c r="C721" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="722">
-      <c r="A722" t="inlineStr">
-        <is>
-          <t>F8_0703_721</t>
-        </is>
-      </c>
-      <c r="B722" t="n">
-        <v>134</v>
-      </c>
-      <c r="C722" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="723">
-      <c r="A723" t="inlineStr">
-        <is>
-          <t>F8_0703_722</t>
-        </is>
-      </c>
-      <c r="B723" t="n">
-        <v>133</v>
-      </c>
-      <c r="C723" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="724">
-      <c r="A724" t="inlineStr">
-        <is>
-          <t>F8_0703_723</t>
-        </is>
-      </c>
-      <c r="B724" t="n">
-        <v>128</v>
-      </c>
-      <c r="C724" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="725">
-      <c r="A725" t="inlineStr">
-        <is>
-          <t>F8_0703_724</t>
-        </is>
-      </c>
-      <c r="B725" t="n">
-        <v>134</v>
-      </c>
-      <c r="C725" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="726">
-      <c r="A726" t="inlineStr">
-        <is>
-          <t>F8_0703_725</t>
-        </is>
-      </c>
-      <c r="B726" t="n">
-        <v>116</v>
-      </c>
-      <c r="C726" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="727">
-      <c r="A727" t="inlineStr">
-        <is>
-          <t>F8_0703_726</t>
-        </is>
-      </c>
-      <c r="B727" t="n">
-        <v>149</v>
-      </c>
-      <c r="C727" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="728">
-      <c r="A728" t="inlineStr">
-        <is>
-          <t>F8_0703_727</t>
-        </is>
-      </c>
-      <c r="B728" t="n">
-        <v>157</v>
-      </c>
-      <c r="C728" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="729">
-      <c r="A729" t="inlineStr">
-        <is>
-          <t>F8_0703_728</t>
-        </is>
-      </c>
-      <c r="B729" t="n">
-        <v>119</v>
-      </c>
-      <c r="C729" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="730">
-      <c r="A730" t="inlineStr">
-        <is>
-          <t>F8_0703_729</t>
-        </is>
-      </c>
-      <c r="B730" t="n">
-        <v>132</v>
-      </c>
-      <c r="C730" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="731">
-      <c r="A731" t="inlineStr">
-        <is>
-          <t>F8_0703_730</t>
-        </is>
-      </c>
-      <c r="B731" t="n">
-        <v>124</v>
-      </c>
-      <c r="C731" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="732">
-      <c r="A732" t="inlineStr">
-        <is>
-          <t>F8_0703_731</t>
-        </is>
-      </c>
-      <c r="B732" t="n">
-        <v>106</v>
-      </c>
-      <c r="C732" t="n">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="733">
-      <c r="A733" t="inlineStr">
-        <is>
-          <t>F8_0703_732</t>
-        </is>
-      </c>
-      <c r="B733" t="n">
-        <v>84</v>
-      </c>
-      <c r="C733" t="n">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="734">
-      <c r="A734" t="inlineStr">
-        <is>
-          <t>F8_0703_733</t>
-        </is>
-      </c>
-      <c r="B734" t="n">
-        <v>81</v>
-      </c>
-      <c r="C734" t="n">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="735">
-      <c r="A735" t="inlineStr">
-        <is>
-          <t>F8_0703_734</t>
-        </is>
-      </c>
-      <c r="B735" t="n">
-        <v>124</v>
-      </c>
-      <c r="C735" t="n">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="736">
-      <c r="A736" t="inlineStr">
-        <is>
-          <t>F8_0703_735</t>
-        </is>
-      </c>
-      <c r="B736" t="n">
-        <v>97</v>
-      </c>
-      <c r="C736" t="n">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="737">
-      <c r="A737" t="inlineStr">
-        <is>
-          <t>F8_0703_736</t>
-        </is>
-      </c>
-      <c r="B737" t="n">
-        <v>123</v>
-      </c>
-      <c r="C737" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="738">
-      <c r="A738" t="inlineStr">
-        <is>
-          <t>F8_0703_737</t>
-        </is>
-      </c>
-      <c r="B738" t="n">
-        <v>104</v>
-      </c>
-      <c r="C738" t="n">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="739">
-      <c r="A739" t="inlineStr">
-        <is>
-          <t>F8_0703_738</t>
-        </is>
-      </c>
-      <c r="B739" t="n">
-        <v>103</v>
-      </c>
-      <c r="C739" t="n">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="740">
-      <c r="A740" t="inlineStr">
-        <is>
-          <t>F8_0703_739</t>
-        </is>
-      </c>
-      <c r="B740" t="n">
-        <v>105</v>
-      </c>
-      <c r="C740" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="741">
-      <c r="A741" t="inlineStr">
-        <is>
-          <t>F8_0703_740</t>
-        </is>
-      </c>
-      <c r="B741" t="n">
-        <v>158</v>
-      </c>
-      <c r="C741" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="742">
-      <c r="A742" t="inlineStr">
-        <is>
-          <t>F8_0703_741</t>
-        </is>
-      </c>
-      <c r="B742" t="n">
-        <v>86</v>
-      </c>
-      <c r="C742" t="n">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="743">
-      <c r="A743" t="inlineStr">
-        <is>
-          <t>F8_0703_742</t>
-        </is>
-      </c>
-      <c r="B743" t="n">
-        <v>92</v>
-      </c>
-      <c r="C743" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="744">
-      <c r="A744" t="inlineStr">
-        <is>
-          <t>F8_0703_743</t>
-        </is>
-      </c>
-      <c r="B744" t="n">
-        <v>94</v>
-      </c>
-      <c r="C744" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="745">
-      <c r="A745" t="inlineStr">
-        <is>
-          <t>F8_0703_744</t>
-        </is>
-      </c>
-      <c r="B745" t="n">
-        <v>90</v>
-      </c>
-      <c r="C745" t="n">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="746">
-      <c r="A746" t="inlineStr">
-        <is>
-          <t>F8_0703_745</t>
-        </is>
-      </c>
-      <c r="B746" t="n">
-        <v>100</v>
-      </c>
-      <c r="C746" t="n">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="747">
-      <c r="A747" t="inlineStr">
-        <is>
-          <t>F8_0703_746</t>
-        </is>
-      </c>
-      <c r="B747" t="n">
-        <v>108</v>
-      </c>
-      <c r="C747" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="748">
-      <c r="A748" t="inlineStr">
-        <is>
-          <t>F8_0703_747</t>
-        </is>
-      </c>
-      <c r="B748" t="n">
-        <v>92</v>
-      </c>
-      <c r="C748" t="n">
-        <v>25</v>
       </c>
     </row>
   </sheetData>
